--- a/月報/N/2025y LP-N 月報表格 - 複製.xlsx
+++ b/月報/N/2025y LP-N 月報表格 - 複製.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JYLIN\Desktop\ni\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JYLIN\Desktop\gh\月報\N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FB4AF2-F991-43F4-8B73-8A7E0259F330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B426C669-6D2B-430C-878B-134BEE5C42CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EF8ECB5-68E2-4B1C-8F0C-12438D926500}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{2EF8ECB5-68E2-4B1C-8F0C-12438D926500}"/>
   </bookViews>
   <sheets>
     <sheet name="2024 Poly PTC 統計" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="247">
   <si>
     <t>Target</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -593,21 +593,6 @@
     <t>2024y 平均RUN數</t>
   </si>
   <si>
-    <t>P6</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
     <t>PTC次數</t>
   </si>
   <si>
@@ -898,6 +883,36 @@
   </si>
   <si>
     <t>q1</t>
+  </si>
+  <si>
+    <t>LP-N2</t>
+  </si>
+  <si>
+    <t>LP-N6</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
+  <si>
+    <t>N2</t>
+  </si>
+  <si>
+    <t>N3</t>
+  </si>
+  <si>
+    <t>N4</t>
+  </si>
+  <si>
+    <t>N5</t>
+  </si>
+  <si>
+    <t>N6</t>
+  </si>
+  <si>
+    <t>N7</t>
+  </si>
+  <si>
+    <t>M/D%</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1363,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -1602,6 +1617,18 @@
     <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1610,15 +1637,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4176,7 +4194,7 @@
                 <a:latin typeface="微軟正黑體"/>
                 <a:ea typeface="微軟正黑體"/>
               </a:rPr>
-              <a:t>4</a:t>
+              <a:t>5</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
@@ -4186,7 +4204,27 @@
                 <a:latin typeface="微軟正黑體"/>
                 <a:ea typeface="微軟正黑體"/>
               </a:rPr>
-              <a:t>y Poly PTC OOS 機台</a:t>
+              <a:t>y </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="微軟正黑體"/>
+                <a:ea typeface="微軟正黑體"/>
+              </a:rPr>
+              <a:t>LP-N</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="333333"/>
+                </a:solidFill>
+                <a:latin typeface="微軟正黑體"/>
+                <a:ea typeface="微軟正黑體"/>
+              </a:rPr>
+              <a:t> PTC OOS 機台</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4215,7 +4253,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>P6</c:v>
+                  <c:v>N7</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4223,222 +4261,6 @@
           <c:spPr>
             <a:solidFill>
               <a:srgbClr val="5B9BD5"/>
-            </a:solidFill>
-            <a:ln w="25400">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="25400">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2024 Poly PTC zone別'!$R$2:$AC$2</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1月</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2月</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3月</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4月</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5月</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6月</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7月</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8月</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9月</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10月</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11月</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12月</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2024 Poly PTC zone別'!$R$3:$AC$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C0C6-4A5D-8CB4-0F47F5E61302}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2024 Poly PTC zone別'!$Q$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>P4</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln w="25400">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="25400">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2024 Poly PTC zone別'!$R$2:$AC$2</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1月</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2月</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3月</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4月</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5月</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6月</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7月</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8月</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9月</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10月</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11月</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12月</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2024 Poly PTC zone別'!$R$4:$AC$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C0C6-4A5D-8CB4-0F47F5E61302}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2024 Poly PTC zone別'!$Q$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>P3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="A5A5A5"/>
             </a:solidFill>
             <a:ln w="25400">
               <a:noFill/>
@@ -4491,21 +4313,119 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2024 Poly PTC zone別'!$R$5:$AC$5</c:f>
+              <c:f>'2024 Poly PTC zone別'!$R$3:$AC$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C0C6-4A5D-8CB4-0F47F5E61302}"/>
+              <c16:uniqueId val="{00000000-C0C6-4A5D-8CB4-0F47F5E61302}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
+          <c:idx val="6"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>N6</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'2024 Poly PTC zone別'!$R$4:$AC$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1D4E-4EAA-89E6-1C6CB2C219AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>N5</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'2024 Poly PTC zone別'!$R$5:$AC$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1D4E-4EAA-89E6-1C6CB2C219AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
@@ -4513,7 +4433,147 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>P2</c:v>
+                  <c:v>N4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2024 Poly PTC zone別'!$R$2:$AC$2</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2月</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3月</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5月</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6月</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7月</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9月</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10月</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11月</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2024 Poly PTC zone別'!$R$6:$AC$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C0C6-4A5D-8CB4-0F47F5E61302}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>N3</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'2024 Poly PTC zone別'!$R$7:$AC$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1D4E-4EAA-89E6-1C6CB2C219AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2024 Poly PTC zone別'!$Q$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>N2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4527,46 +4587,6 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="25400">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="微軟正黑體" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-                    <a:ea typeface="微軟正黑體" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'2024 Poly PTC zone別'!$R$2:$AC$2</c:f>
@@ -4613,12 +4633,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2024 Poly PTC zone別'!$R$6:$AC$6</c:f>
+              <c:f>'2024 Poly PTC zone別'!$R$8:$AC$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4631,14 +4666,14 @@
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>'2024 Poly PTC zone別'!$Q$7</c:f>
+              <c:f>'2024 Poly PTC zone別'!$Q$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>P1</c:v>
+                  <c:v>N1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4652,27 +4687,6 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'2024 Poly PTC zone別'!$R$2:$AC$2</c:f>
@@ -4719,15 +4733,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2024 Poly PTC zone別'!$R$7:$AC$7</c:f>
+              <c:f>'2024 Poly PTC zone別'!$R$9:$AC$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="10">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>6</c:v>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4806,6 +4832,7 @@
         <c:axId val="1"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4892,6 +4919,7 @@
         <c:crossAx val="1110682016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
       </c:valAx>
       <c:dTable>
         <c:showHorzBorder val="1"/>
@@ -13166,13 +13194,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>272143</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>68037</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -19785,17 +19813,25 @@
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
       <c r="Q3" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
+        <v>245</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
+      </c>
+      <c r="S3" s="7">
+        <v>0</v>
+      </c>
       <c r="T3" s="7">
-        <v>1</v>
-      </c>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="U3" s="7">
+        <v>0</v>
+      </c>
+      <c r="V3" s="7">
+        <v>0</v>
+      </c>
       <c r="W3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -19821,24 +19857,32 @@
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="Q4" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
+        <v>244</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0</v>
+      </c>
+      <c r="T4" s="7">
+        <v>0</v>
+      </c>
+      <c r="U4" s="7">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7">
+        <v>0</v>
+      </c>
+      <c r="W4" s="7">
+        <v>1</v>
+      </c>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
-      <c r="AB4" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
     </row>
     <row r="5" spans="2:36" ht="15.75">
       <c r="B5" s="7" t="s">
@@ -19857,14 +19901,26 @@
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="Q5" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
+        <v>243</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7">
+        <v>0</v>
+      </c>
+      <c r="T5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7">
+        <v>0</v>
+      </c>
+      <c r="W5" s="7">
+        <v>0</v>
+      </c>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
@@ -19890,22 +19946,32 @@
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
+        <v>242</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
+      </c>
+      <c r="S6" s="7">
+        <v>0</v>
+      </c>
+      <c r="T6" s="7">
+        <v>0</v>
+      </c>
+      <c r="U6" s="7">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7">
+        <v>0</v>
+      </c>
+      <c r="W6" s="7">
+        <v>0</v>
+      </c>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="7">
-        <v>2</v>
-      </c>
+      <c r="AC6" s="7"/>
       <c r="AJ6" s="49"/>
     </row>
     <row r="7" spans="2:36">
@@ -19925,24 +19991,32 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="Q7" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
+        <v>241</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+      <c r="S7" s="7">
+        <v>0</v>
+      </c>
+      <c r="T7" s="7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7">
+        <v>1</v>
+      </c>
+      <c r="V7" s="7">
+        <v>0</v>
+      </c>
+      <c r="W7" s="7">
+        <v>0</v>
+      </c>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="7">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="7">
-        <v>6</v>
-      </c>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
     </row>
     <row r="8" spans="2:36">
       <c r="B8" s="7" t="s">
@@ -19961,56 +20035,32 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="Q8" s="7" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="R8" s="7">
-        <f>SUM(R3:R7)</f>
         <v>0</v>
       </c>
       <c r="S8" s="7">
-        <f t="shared" ref="S8:AC8" si="0">SUM(S3:S7)</f>
         <v>0</v>
       </c>
       <c r="T8" s="7">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7">
         <v>1</v>
       </c>
-      <c r="U8" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X8" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB8" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AC8" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
     </row>
     <row r="9" spans="2:36">
       <c r="B9" s="7" t="s">
@@ -20029,44 +20079,32 @@
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="Q9" s="7" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="R9" s="7">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="S9" s="7">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="T9" s="7">
-        <v>546</v>
+        <v>0</v>
       </c>
       <c r="U9" s="7">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="V9" s="7">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="W9" s="7">
-        <v>592</v>
-      </c>
-      <c r="X9" s="7">
-        <v>528</v>
-      </c>
-      <c r="Y9" s="7">
-        <v>504</v>
-      </c>
-      <c r="Z9" s="7">
-        <v>483</v>
-      </c>
-      <c r="AA9" s="7">
-        <v>467</v>
-      </c>
-      <c r="AB9" s="7">
-        <v>443</v>
-      </c>
-      <c r="AC9" s="7">
-        <v>471</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
     </row>
     <row r="10" spans="2:36">
       <c r="B10" s="7" t="s">
@@ -20084,6 +20122,57 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
+      <c r="Q10" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="R10" s="7">
+        <f t="shared" ref="R10:AC10" si="0">SUM(R3:R9)</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="2:36">
       <c r="B11" s="7" t="s">
@@ -20101,6 +20190,33 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
+      <c r="Q11" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="R11" s="7">
+        <v>451</v>
+      </c>
+      <c r="S11" s="7">
+        <v>335</v>
+      </c>
+      <c r="T11" s="7">
+        <v>535</v>
+      </c>
+      <c r="U11" s="7">
+        <v>516</v>
+      </c>
+      <c r="V11" s="7">
+        <v>525</v>
+      </c>
+      <c r="W11" s="7">
+        <v>318</v>
+      </c>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
     </row>
     <row r="12" spans="2:36">
       <c r="B12" s="7" t="s">
@@ -20243,7 +20359,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>85</v>
@@ -20788,7 +20904,7 @@
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.75" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="18" width="9" style="1"/>
-    <col min="19" max="19" width="9" style="90"/>
+    <col min="19" max="19" width="9" style="87"/>
     <col min="20" max="25" width="9" style="1"/>
     <col min="29" max="16384" width="9" style="1"/>
   </cols>
@@ -21065,20 +21181,20 @@
       <c r="N10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="88" t="s">
+      <c r="O10" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="P10" s="88" t="s">
+      <c r="P10" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="Q10" s="88" t="s">
+      <c r="Q10" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="R10" s="89" t="s">
+      <c r="R10" s="86" t="s">
         <v>49</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T10" s="7" t="s">
         <v>45</v>
@@ -21086,7 +21202,7 @@
       <c r="U10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="V10" s="88" t="s">
+      <c r="V10" s="85" t="s">
         <v>48</v>
       </c>
       <c r="W10" s="7" t="s">
@@ -21101,7 +21217,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="N11" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O11" s="7">
         <v>49.7</v>
@@ -21177,7 +21293,7 @@
         <v>43</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O12" s="7">
         <v>48</v>
@@ -21251,7 +21367,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="O13" s="7">
         <v>66.3</v>
@@ -21325,7 +21441,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="O14" s="7">
         <v>63.3</v>
@@ -21399,7 +21515,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O15" s="7">
         <v>45.4</v>
@@ -21496,27 +21612,27 @@
         <v>12.12</v>
       </c>
       <c r="T16" s="7">
-        <f>AVERAGE(T11:T15)</f>
+        <f t="shared" ref="T16:Y16" si="3">AVERAGE(T11:T15)</f>
         <v>10.54</v>
       </c>
       <c r="U16" s="7">
-        <f>AVERAGE(U11:U15)</f>
+        <f t="shared" si="3"/>
         <v>1.58</v>
       </c>
       <c r="V16" s="7">
-        <f>AVERAGE(V11:V15)</f>
+        <f t="shared" si="3"/>
         <v>3.3800000000000003</v>
       </c>
       <c r="W16" s="7">
-        <f>AVERAGE(W11:W15)</f>
+        <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
       <c r="X16" s="7">
-        <f>AVERAGE(X11:X15)</f>
+        <f t="shared" si="3"/>
         <v>6.7200000000000006</v>
       </c>
       <c r="Y16" s="7">
-        <f>AVERAGE(Y11:Y15)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -21561,43 +21677,43 @@
         <v>37</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:L18" si="3">AVERAGE(C13:C17)</f>
+        <f t="shared" ref="C18:L18" si="4">AVERAGE(C13:C17)</f>
         <v>80.900000000000006</v>
       </c>
       <c r="D18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.5200000000000005</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.22</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>89.639999999999986</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.12</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.48</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.06</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.3600000000000003</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N18" s="1">
@@ -21608,20 +21724,20 @@
       <c r="N19" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="O19" s="88" t="s">
+      <c r="O19" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="P19" s="88" t="s">
+      <c r="P19" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="Q19" s="88" t="s">
+      <c r="Q19" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="R19" s="89" t="s">
+      <c r="R19" s="86" t="s">
         <v>49</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>45</v>
@@ -21629,7 +21745,7 @@
       <c r="U19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="V19" s="88" t="s">
+      <c r="V19" s="85" t="s">
         <v>48</v>
       </c>
       <c r="W19" s="7" t="s">
@@ -21644,7 +21760,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="N20" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O20" s="7">
         <v>45.2</v>
@@ -21684,7 +21800,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="N21" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O21" s="7">
         <v>48.9</v>
@@ -21696,7 +21812,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="R21" s="7">
-        <f t="shared" ref="R21:R24" si="4">SUM(O21+P21+Q21)</f>
+        <f t="shared" ref="R21:R24" si="5">SUM(O21+P21+Q21)</f>
         <v>83.199999999999989</v>
       </c>
       <c r="S21" s="7">
@@ -21760,7 +21876,7 @@
         <v>43</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="O22" s="7">
         <v>57.9</v>
@@ -21772,7 +21888,7 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>91.600000000000009</v>
       </c>
       <c r="S22" s="7">
@@ -21834,7 +21950,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="O23" s="7">
         <v>30.4</v>
@@ -21846,7 +21962,7 @@
         <v>0.7</v>
       </c>
       <c r="R23" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>89.600000000000009</v>
       </c>
       <c r="S23" s="7">
@@ -21908,7 +22024,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O24" s="7">
         <v>29.2</v>
@@ -21920,7 +22036,7 @@
         <v>0.1</v>
       </c>
       <c r="R24" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>97.8</v>
       </c>
       <c r="S24" s="7">
@@ -21989,43 +22105,43 @@
         <v>42.32</v>
       </c>
       <c r="P25" s="7">
-        <f t="shared" ref="P25" si="5">AVERAGE(P20:P24)</f>
+        <f t="shared" ref="P25" si="6">AVERAGE(P20:P24)</f>
         <v>45.32</v>
       </c>
       <c r="Q25" s="7">
-        <f t="shared" ref="Q25" si="6">AVERAGE(Q20:Q24)</f>
+        <f t="shared" ref="Q25" si="7">AVERAGE(Q20:Q24)</f>
         <v>2.3399999999999994</v>
       </c>
       <c r="R25" s="7">
-        <f t="shared" ref="R25" si="7">AVERAGE(R20:R24)</f>
+        <f t="shared" ref="R25" si="8">AVERAGE(R20:R24)</f>
         <v>89.98</v>
       </c>
       <c r="S25" s="7">
-        <f t="shared" ref="S25" si="8">AVERAGE(S20:S24)</f>
+        <f t="shared" ref="S25" si="9">AVERAGE(S20:S24)</f>
         <v>5.4399999999999995</v>
       </c>
       <c r="T25" s="7">
-        <f t="shared" ref="T25" si="9">AVERAGE(T20:T24)</f>
+        <f t="shared" ref="T25" si="10">AVERAGE(T20:T24)</f>
         <v>4.6399999999999988</v>
       </c>
       <c r="U25" s="7">
-        <f t="shared" ref="U25" si="10">AVERAGE(U20:U24)</f>
+        <f t="shared" ref="U25" si="11">AVERAGE(U20:U24)</f>
         <v>0.8</v>
       </c>
       <c r="V25" s="7">
-        <f t="shared" ref="V25" si="11">AVERAGE(V20:V24)</f>
+        <f t="shared" ref="V25" si="12">AVERAGE(V20:V24)</f>
         <v>4.16</v>
       </c>
       <c r="W25" s="7">
-        <f t="shared" ref="W25" si="12">AVERAGE(W20:W24)</f>
+        <f t="shared" ref="W25" si="13">AVERAGE(W20:W24)</f>
         <v>0</v>
       </c>
       <c r="X25" s="7">
-        <f t="shared" ref="X25" si="13">AVERAGE(X20:X24)</f>
+        <f t="shared" ref="X25" si="14">AVERAGE(X20:X24)</f>
         <v>0.08</v>
       </c>
       <c r="Y25" s="7">
-        <f t="shared" ref="Y25" si="14">AVERAGE(Y20:Y24)</f>
+        <f t="shared" ref="Y25" si="15">AVERAGE(Y20:Y24)</f>
         <v>0</v>
       </c>
     </row>
@@ -22109,62 +22225,62 @@
         <v>37</v>
       </c>
       <c r="C28" s="7">
-        <f t="shared" ref="C28:L28" si="15">AVERAGE(C23:C27)</f>
+        <f t="shared" ref="C28:L28" si="16">AVERAGE(C23:C27)</f>
         <v>78.060000000000016</v>
       </c>
       <c r="D28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.44</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.8200000000000003</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>89.32</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.4799999999999995</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.02</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.48000000000000009</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.42</v>
       </c>
       <c r="K28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L28" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N28" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="O28" s="88" t="s">
+      <c r="O28" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="P28" s="88" t="s">
+      <c r="P28" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="Q28" s="88" t="s">
+      <c r="Q28" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="R28" s="89" t="s">
+      <c r="R28" s="86" t="s">
         <v>49</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T28" s="7" t="s">
         <v>45</v>
@@ -22172,7 +22288,7 @@
       <c r="U28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="V28" s="88" t="s">
+      <c r="V28" s="85" t="s">
         <v>48</v>
       </c>
       <c r="W28" s="7" t="s">
@@ -22187,7 +22303,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="N29" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O29" s="7">
         <v>50.3</v>
@@ -22226,7 +22342,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="N30" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O30" s="7">
         <v>75.099999999999994</v>
@@ -22238,7 +22354,7 @@
         <v>0.9</v>
       </c>
       <c r="R30" s="7">
-        <f t="shared" ref="R30:R33" si="16">SUM(O30:Q30)</f>
+        <f t="shared" ref="R30:R33" si="17">SUM(O30:Q30)</f>
         <v>90.6</v>
       </c>
       <c r="S30" s="7">
@@ -22265,7 +22381,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="N31" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="O31" s="7">
         <v>75.3</v>
@@ -22277,7 +22393,7 @@
         <v>2.4</v>
       </c>
       <c r="R31" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>94.300000000000011</v>
       </c>
       <c r="S31" s="7">
@@ -22340,7 +22456,7 @@
         <v>43</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="O32" s="7">
         <v>54.4</v>
@@ -22352,7 +22468,7 @@
         <v>0</v>
       </c>
       <c r="R32" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>91.699999999999989</v>
       </c>
       <c r="S32" s="7">
@@ -22413,7 +22529,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O33" s="7">
         <v>38.9</v>
@@ -22425,7 +22541,7 @@
         <v>0.4</v>
       </c>
       <c r="R33" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>97.2</v>
       </c>
       <c r="S33" s="7">
@@ -22498,7 +22614,7 @@
         <v>0.8</v>
       </c>
       <c r="R34" s="7">
-        <f t="shared" ref="R34" si="17">AVERAGE(R29:R33)</f>
+        <f t="shared" ref="R34" si="18">AVERAGE(R29:R33)</f>
         <v>91.38</v>
       </c>
       <c r="S34" s="7">
@@ -22631,7 +22747,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -22639,62 +22755,62 @@
         <v>37</v>
       </c>
       <c r="C38" s="7">
-        <f t="shared" ref="C38:L38" si="18">AVERAGE(C33:C37)</f>
+        <f t="shared" ref="C38:L38" si="19">AVERAGE(C33:C37)</f>
         <v>76.64</v>
       </c>
       <c r="D38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.8</v>
       </c>
       <c r="E38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3.1</v>
       </c>
       <c r="F38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>86.54</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.4</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.18</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4.9800000000000013</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.3199999999999998</v>
       </c>
       <c r="L38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N38" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="O38" s="88" t="s">
+      <c r="O38" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="P38" s="88" t="s">
+      <c r="P38" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="Q38" s="88" t="s">
+      <c r="Q38" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="R38" s="89" t="s">
+      <c r="R38" s="86" t="s">
         <v>49</v>
       </c>
       <c r="S38" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T38" s="7" t="s">
         <v>45</v>
@@ -22702,7 +22818,7 @@
       <c r="U38" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="V38" s="88" t="s">
+      <c r="V38" s="85" t="s">
         <v>48</v>
       </c>
       <c r="W38" s="7" t="s">
@@ -22717,148 +22833,148 @@
     </row>
     <row r="39" spans="1:25">
       <c r="N39" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O39" s="51">
         <f>AVERAGE(O11,O20,O29)</f>
         <v>48.4</v>
       </c>
       <c r="P39" s="51">
-        <f t="shared" ref="P39:S39" si="19">AVERAGE(P11,P20,P29)</f>
+        <f t="shared" ref="P39:S39" si="20">AVERAGE(P11,P20,P29)</f>
         <v>36</v>
       </c>
       <c r="Q39" s="51">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.46666666666666673</v>
       </c>
       <c r="R39" s="51">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>84.86666666666666</v>
       </c>
       <c r="S39" s="51">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.5666666666666669</v>
       </c>
       <c r="T39" s="51">
-        <f>AVERAGE(T11,T20,T29)</f>
+        <f t="shared" ref="T39:Y43" si="21">AVERAGE(T11,T20,T29)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="U39" s="51">
-        <f>AVERAGE(U11,U20,U29)</f>
+        <f t="shared" si="21"/>
         <v>1.1666666666666667</v>
       </c>
       <c r="V39" s="51">
-        <f>AVERAGE(V11,V20,V29)</f>
+        <f t="shared" si="21"/>
         <v>8.9333333333333318</v>
       </c>
       <c r="W39" s="51">
-        <f>AVERAGE(W11,W20,W29)</f>
+        <f t="shared" si="21"/>
         <v>0.5</v>
       </c>
       <c r="X39" s="51">
-        <f>AVERAGE(X11,X20,X29)</f>
+        <f t="shared" si="21"/>
         <v>2.8333333333333335</v>
       </c>
       <c r="Y39" s="51">
-        <f>AVERAGE(Y11,Y20,Y29)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:25">
       <c r="N40" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O40" s="51">
-        <f t="shared" ref="O40:S43" si="20">AVERAGE(O12,O21,O30)</f>
+        <f t="shared" ref="O40:S43" si="22">AVERAGE(O12,O21,O30)</f>
         <v>57.333333333333336</v>
       </c>
       <c r="P40" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>19.033333333333335</v>
       </c>
       <c r="Q40" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="R40" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>77.766666666666666</v>
       </c>
       <c r="S40" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>19.333333333333332</v>
       </c>
       <c r="T40" s="51">
-        <f>AVERAGE(T12,T21,T30)</f>
+        <f t="shared" si="21"/>
         <v>18.666666666666668</v>
       </c>
       <c r="U40" s="51">
-        <f>AVERAGE(U12,U21,U30)</f>
+        <f t="shared" si="21"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="V40" s="51">
-        <f>AVERAGE(V12,V21,V30)</f>
+        <f t="shared" si="21"/>
         <v>2.6333333333333333</v>
       </c>
       <c r="W40" s="51">
-        <f>AVERAGE(W12,W21,W30)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="X40" s="51">
-        <f>AVERAGE(X12,X21,X30)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Y40" s="51">
-        <f>AVERAGE(Y12,Y21,Y30)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:25">
       <c r="N41" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="O41" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>66.5</v>
       </c>
       <c r="P41" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>19.633333333333333</v>
       </c>
       <c r="Q41" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4.3666666666666663</v>
       </c>
       <c r="R41" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>90.5</v>
       </c>
       <c r="S41" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="T41" s="51">
-        <f>AVERAGE(T13,T22,T31)</f>
+        <f t="shared" si="21"/>
         <v>3.3666666666666667</v>
       </c>
       <c r="U41" s="51">
-        <f>AVERAGE(U13,U22,U31)</f>
+        <f t="shared" si="21"/>
         <v>0.23333333333333331</v>
       </c>
       <c r="V41" s="51">
-        <f>AVERAGE(V13,V22,V31)</f>
+        <f t="shared" si="21"/>
         <v>2.6333333333333333</v>
       </c>
       <c r="W41" s="51">
-        <f>AVERAGE(W13,W22,W31)</f>
+        <f t="shared" si="21"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="X41" s="51">
-        <f>AVERAGE(X13,X22,X31)</f>
+        <f t="shared" si="21"/>
         <v>2.8333333333333335</v>
       </c>
       <c r="Y41" s="51">
-        <f>AVERAGE(Y13,Y22,Y31)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -22900,50 +23016,50 @@
         <v>43</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="O42" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>49.366666666666667</v>
       </c>
       <c r="P42" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>40.666666666666664</v>
       </c>
       <c r="Q42" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.23333333333333331</v>
       </c>
       <c r="R42" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>90.266666666666666</v>
       </c>
       <c r="S42" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4.5666666666666664</v>
       </c>
       <c r="T42" s="51">
-        <f>AVERAGE(T14,T23,T32)</f>
+        <f t="shared" si="21"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="U42" s="51">
-        <f>AVERAGE(U14,U23,U32)</f>
+        <f t="shared" si="21"/>
         <v>2.2666666666666666</v>
       </c>
       <c r="V42" s="51">
-        <f>AVERAGE(V14,V23,V32)</f>
+        <f t="shared" si="21"/>
         <v>1.9666666666666668</v>
       </c>
       <c r="W42" s="51">
-        <f>AVERAGE(W14,W23,W32)</f>
+        <f t="shared" si="21"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="X42" s="51">
-        <f>AVERAGE(X14,X23,X32)</f>
+        <f t="shared" si="21"/>
         <v>2.8333333333333335</v>
       </c>
       <c r="Y42" s="51">
-        <f>AVERAGE(Y14,Y23,Y32)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -22983,50 +23099,50 @@
         <v>0</v>
       </c>
       <c r="N43" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O43" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>37.833333333333336</v>
       </c>
       <c r="P43" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>49.633333333333333</v>
       </c>
       <c r="Q43" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.23333333333333336</v>
       </c>
       <c r="R43" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>87.7</v>
       </c>
       <c r="S43" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>6.2666666666666657</v>
       </c>
       <c r="T43" s="51">
-        <f>AVERAGE(T15,T24,T33)</f>
+        <f t="shared" si="21"/>
         <v>3.7333333333333329</v>
       </c>
       <c r="U43" s="51">
-        <f>AVERAGE(U15,U24,U33)</f>
+        <f t="shared" si="21"/>
         <v>2.5333333333333337</v>
       </c>
       <c r="V43" s="51">
-        <f>AVERAGE(V15,V24,V33)</f>
+        <f t="shared" si="21"/>
         <v>2.7666666666666671</v>
       </c>
       <c r="W43" s="51">
-        <f>AVERAGE(W15,W24,W33)</f>
+        <f t="shared" si="21"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="X43" s="51">
-        <f>AVERAGE(X15,X24,X33)</f>
+        <f t="shared" si="21"/>
         <v>2.8333333333333335</v>
       </c>
       <c r="Y43" s="51">
-        <f>AVERAGE(Y15,Y24,Y33)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -23073,43 +23189,43 @@
         <v>51.88666666666667</v>
       </c>
       <c r="P44" s="51">
-        <f t="shared" ref="P44" si="21">AVERAGE(P39:P43)</f>
+        <f t="shared" ref="P44" si="23">AVERAGE(P39:P43)</f>
         <v>32.993333333333325</v>
       </c>
       <c r="Q44" s="51">
-        <f t="shared" ref="Q44" si="22">AVERAGE(Q39:Q43)</f>
+        <f t="shared" ref="Q44" si="24">AVERAGE(Q39:Q43)</f>
         <v>1.34</v>
       </c>
       <c r="R44" s="51">
-        <f t="shared" ref="R44" si="23">AVERAGE(R39:R43)</f>
+        <f t="shared" ref="R44" si="25">AVERAGE(R39:R43)</f>
         <v>86.22</v>
       </c>
       <c r="S44" s="51">
-        <f t="shared" ref="S44" si="24">AVERAGE(S39:S43)</f>
+        <f t="shared" ref="S44" si="26">AVERAGE(S39:S43)</f>
         <v>7.2666666666666657</v>
       </c>
       <c r="T44" s="51">
-        <f t="shared" ref="T44" si="25">AVERAGE(T39:T43)</f>
+        <f t="shared" ref="T44" si="27">AVERAGE(T39:T43)</f>
         <v>5.8933333333333335</v>
       </c>
       <c r="U44" s="51">
-        <f t="shared" ref="U44" si="26">AVERAGE(U39:U43)</f>
+        <f t="shared" ref="U44" si="28">AVERAGE(U39:U43)</f>
         <v>1.3733333333333335</v>
       </c>
       <c r="V44" s="51">
-        <f t="shared" ref="V44" si="27">AVERAGE(V39:V43)</f>
+        <f t="shared" ref="V44" si="29">AVERAGE(V39:V43)</f>
         <v>3.7866666666666662</v>
       </c>
       <c r="W44" s="51">
-        <f t="shared" ref="W44" si="28">AVERAGE(W39:W43)</f>
+        <f t="shared" ref="W44" si="30">AVERAGE(W39:W43)</f>
         <v>0.15333333333333332</v>
       </c>
       <c r="X44" s="51">
-        <f t="shared" ref="X44" si="29">AVERAGE(X39:X43)</f>
+        <f t="shared" ref="X44" si="31">AVERAGE(X39:X43)</f>
         <v>2.2666666666666666</v>
       </c>
       <c r="Y44" s="51">
-        <f t="shared" ref="Y44" si="30">AVERAGE(Y39:Y43)</f>
+        <f t="shared" ref="Y44" si="32">AVERAGE(Y39:Y43)</f>
         <v>0</v>
       </c>
     </row>
@@ -23184,6 +23300,9 @@
       <c r="L46" s="7">
         <v>0</v>
       </c>
+      <c r="N46" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="47" spans="1:25">
       <c r="B47" s="7" t="s">
@@ -23220,53 +23339,243 @@
       <c r="L47" s="7">
         <v>0</v>
       </c>
+      <c r="N47" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O47" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P47" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q47" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R47" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S47" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T47" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V47" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X47" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y47" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="48" spans="1:25">
       <c r="B48" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C48" s="7">
-        <f t="shared" ref="C48:L48" si="31">AVERAGE(C43:C47)</f>
+        <f t="shared" ref="C48:L48" si="33">AVERAGE(C43:C47)</f>
         <v>82</v>
       </c>
       <c r="D48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>6.419999999999999</v>
       </c>
       <c r="E48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3.4799999999999995</v>
       </c>
       <c r="F48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>91.9</v>
       </c>
       <c r="G48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3.8200000000000003</v>
       </c>
       <c r="H48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="I48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="J48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3.6599999999999993</v>
       </c>
       <c r="K48" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L48" s="7">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O48" s="88">
+        <v>63.3</v>
+      </c>
+      <c r="P48" s="88">
+        <v>36.6</v>
+      </c>
+      <c r="Q48" s="88">
+        <v>0</v>
+      </c>
+      <c r="R48" s="51">
+        <f>SUM(O48:Q48)</f>
+        <v>99.9</v>
+      </c>
+      <c r="S48" s="88">
+        <v>0</v>
+      </c>
+      <c r="T48" s="88">
+        <v>0</v>
+      </c>
+      <c r="U48" s="88">
+        <v>0</v>
+      </c>
+      <c r="V48" s="88">
+        <v>0</v>
+      </c>
+      <c r="W48" s="88">
+        <v>0</v>
+      </c>
+      <c r="X48" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28">
+      <c r="N49" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O49" s="88">
+        <v>50.4</v>
+      </c>
+      <c r="P49" s="88">
+        <v>28</v>
+      </c>
+      <c r="Q49" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="R49" s="51">
+        <f t="shared" ref="R49:R54" si="34">SUM(O49:Q49)</f>
+        <v>78.5</v>
+      </c>
+      <c r="S49" s="88">
+        <v>1.5</v>
+      </c>
+      <c r="T49" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="U49" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="V49" s="88">
+        <v>6.2</v>
+      </c>
+      <c r="W49" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="X49" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="88">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28">
+      <c r="N50" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O50" s="88">
+        <v>80.8</v>
+      </c>
+      <c r="P50" s="88">
+        <v>7.9</v>
+      </c>
+      <c r="Q50" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="R50" s="51">
+        <f t="shared" si="34"/>
+        <v>88.8</v>
+      </c>
+      <c r="S50" s="88">
+        <v>5.7</v>
+      </c>
+      <c r="T50" s="88">
+        <v>0</v>
+      </c>
+      <c r="U50" s="88">
+        <v>5.4</v>
+      </c>
+      <c r="V50" s="88">
+        <v>5.5</v>
+      </c>
+      <c r="W50" s="88">
+        <v>0</v>
+      </c>
+      <c r="X50" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28">
+      <c r="N51" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O51" s="88">
+        <v>77.8</v>
+      </c>
+      <c r="P51" s="88">
+        <v>13.1</v>
+      </c>
+      <c r="Q51" s="88">
+        <v>0</v>
+      </c>
+      <c r="R51" s="51">
+        <f t="shared" si="34"/>
+        <v>90.899999999999991</v>
+      </c>
+      <c r="S51" s="88">
+        <v>4.7</v>
+      </c>
+      <c r="T51" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="U51" s="88">
+        <v>4</v>
+      </c>
+      <c r="V51" s="88">
+        <v>4.3</v>
+      </c>
+      <c r="W51" s="88">
+        <v>0</v>
+      </c>
+      <c r="X51" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28">
       <c r="A52" s="1" t="s">
         <v>61</v>
       </c>
@@ -23303,8 +23612,45 @@
       <c r="L52" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="N52" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O52" s="88">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="P52" s="88">
+        <v>23.4</v>
+      </c>
+      <c r="Q52" s="88">
+        <v>1.5</v>
+      </c>
+      <c r="R52" s="51">
+        <f t="shared" si="34"/>
+        <v>92.300000000000011</v>
+      </c>
+      <c r="S52" s="88">
+        <v>4.8</v>
+      </c>
+      <c r="T52" s="88">
+        <v>0</v>
+      </c>
+      <c r="U52" s="88">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="V52" s="88">
+        <v>2.8</v>
+      </c>
+      <c r="W52" s="88">
+        <v>0</v>
+      </c>
+      <c r="X52" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28">
       <c r="B53" s="7" t="s">
         <v>42</v>
       </c>
@@ -23339,8 +23685,45 @@
       <c r="L53" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="N53" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O53" s="88">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="P53" s="88">
+        <v>31.6</v>
+      </c>
+      <c r="Q53" s="88">
+        <v>0</v>
+      </c>
+      <c r="R53" s="51">
+        <f t="shared" si="34"/>
+        <v>97.199999999999989</v>
+      </c>
+      <c r="S53" s="88">
+        <v>0</v>
+      </c>
+      <c r="T53" s="88">
+        <v>0</v>
+      </c>
+      <c r="U53" s="88">
+        <v>0</v>
+      </c>
+      <c r="V53" s="88">
+        <v>2.7</v>
+      </c>
+      <c r="W53" s="88">
+        <v>0</v>
+      </c>
+      <c r="X53" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28">
       <c r="B54" s="7" t="s">
         <v>41</v>
       </c>
@@ -23375,8 +23758,45 @@
       <c r="L54" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="N54" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O54" s="88">
+        <v>49.5</v>
+      </c>
+      <c r="P54" s="88">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="Q54" s="88">
+        <v>1</v>
+      </c>
+      <c r="R54" s="51">
+        <f t="shared" si="34"/>
+        <v>88.8</v>
+      </c>
+      <c r="S54" s="88">
+        <v>6</v>
+      </c>
+      <c r="T54" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="U54" s="88">
+        <v>4.2</v>
+      </c>
+      <c r="V54" s="88">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="W54" s="88">
+        <v>0</v>
+      </c>
+      <c r="X54" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28">
       <c r="B55" s="7" t="s">
         <v>40</v>
       </c>
@@ -23411,8 +23831,46 @@
       <c r="L55" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="N55" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" s="88">
+        <v>65</v>
+      </c>
+      <c r="P55" s="88">
+        <v>25.6</v>
+      </c>
+      <c r="Q55" s="88">
+        <v>0.4</v>
+      </c>
+      <c r="R55" s="88">
+        <f>AVERAGE(R48:R54)</f>
+        <v>90.914285714285697</v>
+      </c>
+      <c r="S55" s="88">
+        <f>AVERAGE(S47:S54)</f>
+        <v>3.2428571428571429</v>
+      </c>
+      <c r="T55" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="U55" s="88">
+        <v>2.8</v>
+      </c>
+      <c r="V55" s="88">
+        <v>3.8</v>
+      </c>
+      <c r="W55" s="88">
+        <v>0</v>
+      </c>
+      <c r="X55" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="88">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28">
       <c r="B56" s="7" t="s">
         <v>39</v>
       </c>
@@ -23447,8 +23905,15 @@
       <c r="L56" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="S56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
+    </row>
+    <row r="57" spans="1:28">
       <c r="B57" s="7" t="s">
         <v>38</v>
       </c>
@@ -23483,53 +23948,209 @@
       <c r="L57" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="N57" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28">
       <c r="B58" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C58" s="7">
-        <f t="shared" ref="C58:L58" si="32">AVERAGE(C53:C57)</f>
+        <f t="shared" ref="C58:L58" si="35">AVERAGE(C53:C57)</f>
         <v>80.240000000000009</v>
       </c>
       <c r="D58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>7.4</v>
       </c>
       <c r="E58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>2.4400000000000004</v>
       </c>
       <c r="F58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>90.08</v>
       </c>
       <c r="G58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>4.78</v>
       </c>
       <c r="H58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.06</v>
       </c>
       <c r="I58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="J58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>4.8000000000000007</v>
       </c>
       <c r="K58" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L58" s="7">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="N58" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O58" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P58" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q58" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R58" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S58" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T58" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V58" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W58" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X58" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y58" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28">
+      <c r="N59" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O59" s="88">
+        <v>56</v>
+      </c>
+      <c r="P59" s="88">
+        <v>43.9</v>
+      </c>
+      <c r="Q59" s="88">
+        <v>0</v>
+      </c>
+      <c r="R59" s="51">
+        <f>SUM(O59:Q59)</f>
+        <v>99.9</v>
+      </c>
+      <c r="S59" s="88">
+        <v>0</v>
+      </c>
+      <c r="T59" s="88">
+        <v>0</v>
+      </c>
+      <c r="U59" s="88">
+        <v>0</v>
+      </c>
+      <c r="V59" s="88">
+        <v>0</v>
+      </c>
+      <c r="W59" s="88">
+        <v>0</v>
+      </c>
+      <c r="X59" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28">
+      <c r="N60" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O60" s="88">
+        <v>61.4</v>
+      </c>
+      <c r="P60" s="88">
+        <v>31.2</v>
+      </c>
+      <c r="Q60" s="88">
+        <v>0</v>
+      </c>
+      <c r="R60" s="51">
+        <f t="shared" ref="R60:R65" si="36">SUM(O60:Q60)</f>
+        <v>92.6</v>
+      </c>
+      <c r="S60" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="T60" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="U60" s="88">
+        <v>0</v>
+      </c>
+      <c r="V60" s="88">
+        <v>0</v>
+      </c>
+      <c r="W60" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="X60" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="88">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28">
+      <c r="N61" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O61" s="88">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="P61" s="88">
+        <v>9.5</v>
+      </c>
+      <c r="Q61" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="R61" s="51">
+        <f t="shared" si="36"/>
+        <v>90.399999999999991</v>
+      </c>
+      <c r="S61" s="88">
+        <v>7</v>
+      </c>
+      <c r="T61" s="88">
+        <v>0</v>
+      </c>
+      <c r="U61" s="88">
+        <v>7</v>
+      </c>
+      <c r="V61" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W61" s="88">
+        <v>0</v>
+      </c>
+      <c r="X61" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
@@ -23566,8 +24187,45 @@
       <c r="L62" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="N62" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O62" s="88">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="P62" s="88">
+        <v>15.5</v>
+      </c>
+      <c r="Q62" s="88">
+        <v>0.8</v>
+      </c>
+      <c r="R62" s="51">
+        <f t="shared" si="36"/>
+        <v>84.7</v>
+      </c>
+      <c r="S62" s="88">
+        <v>7.1</v>
+      </c>
+      <c r="T62" s="88">
+        <v>2</v>
+      </c>
+      <c r="U62" s="88">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="V62" s="88">
+        <v>7.8</v>
+      </c>
+      <c r="W62" s="88">
+        <v>0</v>
+      </c>
+      <c r="X62" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28">
       <c r="B63" s="7" t="s">
         <v>42</v>
       </c>
@@ -23602,8 +24260,45 @@
       <c r="L63" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="N63" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O63" s="88">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="P63" s="88">
+        <v>21.7</v>
+      </c>
+      <c r="Q63" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R63" s="51">
+        <f t="shared" si="36"/>
+        <v>89.899999999999991</v>
+      </c>
+      <c r="S63" s="88">
+        <v>6.1</v>
+      </c>
+      <c r="T63" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="U63" s="88">
+        <v>5.4</v>
+      </c>
+      <c r="V63" s="88">
+        <v>3.8</v>
+      </c>
+      <c r="W63" s="88">
+        <v>0</v>
+      </c>
+      <c r="X63" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28">
       <c r="B64" s="7" t="s">
         <v>41</v>
       </c>
@@ -23638,8 +24333,45 @@
       <c r="L64" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="N64" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O64" s="88">
+        <v>44.7</v>
+      </c>
+      <c r="P64" s="88">
+        <v>53</v>
+      </c>
+      <c r="Q64" s="88">
+        <v>0</v>
+      </c>
+      <c r="R64" s="51">
+        <f t="shared" si="36"/>
+        <v>97.7</v>
+      </c>
+      <c r="S64" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="T64" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="U64" s="88">
+        <v>0</v>
+      </c>
+      <c r="V64" s="88">
+        <v>0.8</v>
+      </c>
+      <c r="W64" s="88">
+        <v>0</v>
+      </c>
+      <c r="X64" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25">
       <c r="B65" s="7" t="s">
         <v>40</v>
       </c>
@@ -23674,8 +24406,45 @@
       <c r="L65" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="N65" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O65" s="88">
+        <v>44.9</v>
+      </c>
+      <c r="P65" s="88">
+        <v>46.9</v>
+      </c>
+      <c r="Q65" s="88">
+        <v>0</v>
+      </c>
+      <c r="R65" s="51">
+        <f t="shared" si="36"/>
+        <v>91.8</v>
+      </c>
+      <c r="S65" s="88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="T65" s="88">
+        <v>0</v>
+      </c>
+      <c r="U65" s="88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V65" s="88">
+        <v>3.6</v>
+      </c>
+      <c r="W65" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="X65" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25">
       <c r="B66" s="7" t="s">
         <v>39</v>
       </c>
@@ -23710,8 +24479,45 @@
       <c r="L66" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="N66" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" s="88">
+        <v>60.2</v>
+      </c>
+      <c r="P66" s="88">
+        <v>31.7</v>
+      </c>
+      <c r="Q66" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="R66" s="88">
+        <f>AVERAGE(R59:R65)</f>
+        <v>92.428571428571416</v>
+      </c>
+      <c r="S66" s="88">
+        <v>3.7</v>
+      </c>
+      <c r="T66" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="U66" s="88">
+        <v>3.1</v>
+      </c>
+      <c r="V66" s="88">
+        <v>2.6</v>
+      </c>
+      <c r="W66" s="88">
+        <v>0</v>
+      </c>
+      <c r="X66" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="88">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25">
       <c r="B67" s="7" t="s">
         <v>38</v>
       </c>
@@ -23747,52 +24553,171 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:25">
       <c r="B68" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C68" s="7">
-        <f t="shared" ref="C68:L68" si="33">AVERAGE(C63:C67)</f>
+        <f t="shared" ref="C68:L68" si="37">AVERAGE(C63:C67)</f>
         <v>77.739999999999995</v>
       </c>
       <c r="D68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>9.0400000000000009</v>
       </c>
       <c r="E68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>3.4800000000000004</v>
       </c>
       <c r="F68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>90.26</v>
       </c>
       <c r="G68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>5.24</v>
       </c>
       <c r="H68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="I68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.3</v>
       </c>
       <c r="J68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>3.94</v>
       </c>
       <c r="K68" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L68" s="7">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
+      <c r="N69" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O69" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P69" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q69" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R69" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S69" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T69" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U69" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V69" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W69" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X69" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y69" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="N70" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O70" s="88">
+        <v>59.6</v>
+      </c>
+      <c r="P70" s="88">
+        <v>36.1</v>
+      </c>
+      <c r="Q70" s="88">
+        <v>0</v>
+      </c>
+      <c r="R70" s="51">
+        <f>SUM(O70:Q70)</f>
+        <v>95.7</v>
+      </c>
+      <c r="S70" s="88">
+        <v>0</v>
+      </c>
+      <c r="T70" s="88">
+        <v>2.6</v>
+      </c>
+      <c r="U70" s="88">
+        <v>1.7</v>
+      </c>
+      <c r="V70" s="88">
+        <v>1.5</v>
+      </c>
+      <c r="W70" s="88">
+        <v>0</v>
+      </c>
+      <c r="X70" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25">
+      <c r="N71" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O71" s="88">
+        <v>68.8</v>
+      </c>
+      <c r="P71" s="88">
+        <v>19.7</v>
+      </c>
+      <c r="Q71" s="88">
+        <v>0</v>
+      </c>
+      <c r="R71" s="51">
+        <f t="shared" ref="R71:R76" si="38">SUM(O71:Q71)</f>
+        <v>88.5</v>
+      </c>
+      <c r="S71" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="T71" s="88">
+        <v>4.7</v>
+      </c>
+      <c r="U71" s="88">
+        <v>3.7</v>
+      </c>
+      <c r="V71" s="88">
+        <v>6.6</v>
+      </c>
+      <c r="W71" s="88">
+        <v>0</v>
+      </c>
+      <c r="X71" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25">
       <c r="A72" s="1" t="s">
         <v>4</v>
       </c>
@@ -23829,8 +24754,45 @@
       <c r="L72" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="73" spans="1:12">
+      <c r="N72" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O72" s="88">
+        <v>82.2</v>
+      </c>
+      <c r="P72" s="88">
+        <v>13.1</v>
+      </c>
+      <c r="Q72" s="88">
+        <v>0</v>
+      </c>
+      <c r="R72" s="51">
+        <f t="shared" si="38"/>
+        <v>95.3</v>
+      </c>
+      <c r="S72" s="88">
+        <v>7</v>
+      </c>
+      <c r="T72" s="88">
+        <v>3.6</v>
+      </c>
+      <c r="U72" s="88">
+        <v>3.6</v>
+      </c>
+      <c r="V72" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="W72" s="88">
+        <v>0</v>
+      </c>
+      <c r="X72" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25">
       <c r="B73" s="7" t="s">
         <v>42</v>
       </c>
@@ -23865,8 +24827,45 @@
       <c r="L73" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:12">
+      <c r="N73" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O73" s="88">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="P73" s="88">
+        <v>21.9</v>
+      </c>
+      <c r="Q73" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="R73" s="51">
+        <f t="shared" si="38"/>
+        <v>97.100000000000009</v>
+      </c>
+      <c r="S73" s="88">
+        <v>7.1</v>
+      </c>
+      <c r="T73" s="88">
+        <v>1.5</v>
+      </c>
+      <c r="U73" s="88">
+        <v>1.5</v>
+      </c>
+      <c r="V73" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="W73" s="88">
+        <v>0</v>
+      </c>
+      <c r="X73" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25">
       <c r="B74" s="7" t="s">
         <v>41</v>
       </c>
@@ -23901,8 +24900,45 @@
       <c r="L74" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:12">
+      <c r="N74" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O74" s="88">
+        <v>54.5</v>
+      </c>
+      <c r="P74" s="88">
+        <v>42.3</v>
+      </c>
+      <c r="Q74" s="88">
+        <v>0</v>
+      </c>
+      <c r="R74" s="51">
+        <f t="shared" si="38"/>
+        <v>96.8</v>
+      </c>
+      <c r="S74" s="88">
+        <v>6.1</v>
+      </c>
+      <c r="T74" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="U74" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="V74" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="W74" s="88">
+        <v>0</v>
+      </c>
+      <c r="X74" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25">
       <c r="B75" s="7" t="s">
         <v>40</v>
       </c>
@@ -23937,8 +24973,45 @@
       <c r="L75" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:12">
+      <c r="N75" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O75" s="88">
+        <v>28.4</v>
+      </c>
+      <c r="P75" s="88">
+        <v>46.1</v>
+      </c>
+      <c r="Q75" s="88">
+        <v>0</v>
+      </c>
+      <c r="R75" s="51">
+        <f t="shared" si="38"/>
+        <v>74.5</v>
+      </c>
+      <c r="S75" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="T75" s="88">
+        <v>9.1</v>
+      </c>
+      <c r="U75" s="88">
+        <v>3.1</v>
+      </c>
+      <c r="V75" s="88">
+        <v>16.2</v>
+      </c>
+      <c r="W75" s="88">
+        <v>0</v>
+      </c>
+      <c r="X75" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25">
       <c r="B76" s="7" t="s">
         <v>39</v>
       </c>
@@ -23973,8 +25046,45 @@
       <c r="L76" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:12">
+      <c r="N76" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O76" s="88">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="P76" s="88">
+        <v>60.2</v>
+      </c>
+      <c r="Q76" s="88">
+        <v>0</v>
+      </c>
+      <c r="R76" s="51">
+        <f t="shared" si="38"/>
+        <v>93.9</v>
+      </c>
+      <c r="S76" s="88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="T76" s="88">
+        <v>2.6</v>
+      </c>
+      <c r="U76" s="88">
+        <v>1.7</v>
+      </c>
+      <c r="V76" s="88">
+        <v>3.3</v>
+      </c>
+      <c r="W76" s="88">
+        <v>0</v>
+      </c>
+      <c r="X76" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25">
       <c r="B77" s="7" t="s">
         <v>38</v>
       </c>
@@ -24009,49 +25119,86 @@
       <c r="L77" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:12">
+      <c r="N77" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" s="88">
+        <v>57.3</v>
+      </c>
+      <c r="P77" s="88">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="Q77" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="R77" s="88">
+        <f>AVERAGE(R70:R76)</f>
+        <v>91.685714285714297</v>
+      </c>
+      <c r="S77" s="88">
+        <v>3.7</v>
+      </c>
+      <c r="T77" s="88">
+        <v>3.7</v>
+      </c>
+      <c r="U77" s="88">
+        <v>2.4</v>
+      </c>
+      <c r="V77" s="88">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="W77" s="88">
+        <v>0</v>
+      </c>
+      <c r="X77" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25">
       <c r="B78" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C78" s="7">
-        <f t="shared" ref="C78:L78" si="34">AVERAGE(C73:C77)</f>
+        <f t="shared" ref="C78:L78" si="39">AVERAGE(C73:C77)</f>
         <v>80</v>
       </c>
       <c r="D78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>7.62</v>
       </c>
       <c r="E78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>3.1399999999999997</v>
       </c>
       <c r="F78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>90.76</v>
       </c>
       <c r="G78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="H78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>0.02</v>
       </c>
       <c r="I78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>0.12000000000000002</v>
       </c>
       <c r="J78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>4.16</v>
       </c>
       <c r="K78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="L78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
@@ -24291,27 +25438,27 @@
         <v>90.559999999999988</v>
       </c>
       <c r="G88" s="7">
-        <f t="shared" ref="G88:L88" si="35">AVERAGE(G83:G87)</f>
+        <f t="shared" ref="G88:L88" si="40">AVERAGE(G83:G87)</f>
         <v>4.7200000000000006</v>
       </c>
       <c r="H88" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="I88" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>0.06</v>
       </c>
       <c r="J88" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>4.38</v>
       </c>
       <c r="K88" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="L88" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -24538,43 +25685,43 @@
         <v>37</v>
       </c>
       <c r="C98" s="7">
-        <f t="shared" ref="C98:L98" si="36">AVERAGE(C93:C97)</f>
+        <f t="shared" ref="C98:L98" si="41">AVERAGE(C93:C97)</f>
         <v>79.040000000000006</v>
       </c>
       <c r="D98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="E98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>1.6</v>
       </c>
       <c r="F98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>89.44</v>
       </c>
       <c r="G98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>4.7799999999999994</v>
       </c>
       <c r="H98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="I98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.38</v>
       </c>
       <c r="J98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>4.9599999999999991</v>
       </c>
       <c r="K98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0.1</v>
       </c>
       <c r="L98" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
     </row>
@@ -24801,43 +25948,43 @@
         <v>37</v>
       </c>
       <c r="C108" s="7">
-        <f t="shared" ref="C108:L108" si="37">AVERAGE(C103:C107)</f>
+        <f t="shared" ref="C108:L108" si="42">AVERAGE(C103:C107)</f>
         <v>70.84</v>
       </c>
       <c r="D108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>17.34</v>
       </c>
       <c r="E108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>2.62</v>
       </c>
       <c r="F108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>90.8</v>
       </c>
       <c r="G108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="H108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="I108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="J108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>3.7</v>
       </c>
       <c r="K108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L108" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
@@ -25064,43 +26211,43 @@
         <v>37</v>
       </c>
       <c r="C118" s="7">
-        <f t="shared" ref="C118:L118" si="38">AVERAGE(C113:C117)</f>
+        <f t="shared" ref="C118:L118" si="43">AVERAGE(C113:C117)</f>
         <v>73.539999999999992</v>
       </c>
       <c r="D118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>13.6</v>
       </c>
       <c r="E118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>2.7800000000000002</v>
       </c>
       <c r="F118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>89.919999999999987</v>
       </c>
       <c r="G118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>5.22</v>
       </c>
       <c r="H118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.27999999999999997</v>
       </c>
       <c r="J118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>4.2600000000000007</v>
       </c>
       <c r="K118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="L118" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -25330,43 +26477,43 @@
         <v>37</v>
       </c>
       <c r="C128" s="7">
-        <f t="shared" ref="C128:L128" si="39">AVERAGE(C123:C127)</f>
+        <f t="shared" ref="C128:L128" si="44">AVERAGE(C123:C127)</f>
         <v>68.960000000000008</v>
       </c>
       <c r="D128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>16.28</v>
       </c>
       <c r="E128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>3.16</v>
       </c>
       <c r="F128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>88.4</v>
       </c>
       <c r="G128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>6.7200000000000006</v>
       </c>
       <c r="H128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>0.1</v>
       </c>
       <c r="I128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="J128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>4.28</v>
       </c>
       <c r="K128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L128" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q128" s="1">
@@ -25611,43 +26758,43 @@
         <v>37</v>
       </c>
       <c r="C138" s="7">
-        <f t="shared" ref="C138:L138" si="40">AVERAGE(C133:C137)</f>
+        <f t="shared" ref="C138:L138" si="45">AVERAGE(C133:C137)</f>
         <v>79.22</v>
       </c>
       <c r="D138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>7.6199999999999992</v>
       </c>
       <c r="E138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>2.68</v>
       </c>
       <c r="F138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>89.52</v>
       </c>
       <c r="G138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>6.02</v>
       </c>
       <c r="H138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="I138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0.42000000000000004</v>
       </c>
       <c r="J138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>3.7600000000000002</v>
       </c>
       <c r="K138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L138" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
     </row>
@@ -25874,43 +27021,43 @@
         <v>37</v>
       </c>
       <c r="C148" s="7">
-        <f t="shared" ref="C148:L148" si="41">AVERAGE(C143:C147)</f>
+        <f t="shared" ref="C148:L148" si="46">AVERAGE(C143:C147)</f>
         <v>79.540000000000006</v>
       </c>
       <c r="D148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>8.58</v>
       </c>
       <c r="E148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>3.3200000000000003</v>
       </c>
       <c r="F148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>91.439999999999984</v>
       </c>
       <c r="G148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>3.88</v>
       </c>
       <c r="H148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="I148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>6.0000000000000012E-2</v>
       </c>
       <c r="J148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>3.3200000000000003</v>
       </c>
       <c r="K148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="L148" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
     </row>
@@ -26137,43 +27284,43 @@
         <v>37</v>
       </c>
       <c r="C158" s="7">
-        <f t="shared" ref="C158:L158" si="42">AVERAGE(C153:C157)</f>
+        <f t="shared" ref="C158:L158" si="47">AVERAGE(C153:C157)</f>
         <v>79.459999999999994</v>
       </c>
       <c r="D158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>6.8400000000000007</v>
       </c>
       <c r="E158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>2.8</v>
       </c>
       <c r="F158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>89.1</v>
       </c>
       <c r="G158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>5.78</v>
       </c>
       <c r="H158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="I158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>0.74</v>
       </c>
       <c r="J158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>3.7399999999999998</v>
       </c>
       <c r="K158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L158" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
@@ -26215,7 +27362,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>85</v>
@@ -26528,387 +27675,387 @@
   <sheetData>
     <row r="1" spans="2:12">
       <c r="B1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" t="s">
         <v>148</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>149</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>150</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>151</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>152</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>153</v>
-      </c>
-      <c r="H1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" t="s">
-        <v>156</v>
-      </c>
-      <c r="K1" t="s">
-        <v>157</v>
-      </c>
-      <c r="L1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="2" spans="2:12">
       <c r="B2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F2">
         <v>5.35</v>
       </c>
       <c r="G2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="2:12">
       <c r="B3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F3">
         <v>0.25</v>
       </c>
       <c r="G3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="K3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="L3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:12">
       <c r="B4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" t="s">
         <v>191</v>
       </c>
-      <c r="D4" t="s">
-        <v>196</v>
-      </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F4">
         <v>0.65</v>
       </c>
       <c r="G4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="L4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:12">
       <c r="B5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F5">
         <v>2.95</v>
       </c>
       <c r="G5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="K5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="L5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="B6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F6">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="2:12">
       <c r="B7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F7">
         <v>2.17</v>
       </c>
       <c r="G7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J7" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="K7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="2:12">
       <c r="B8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F8">
         <v>2.17</v>
       </c>
       <c r="G8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="2:12">
       <c r="B9" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F9">
         <v>2.17</v>
       </c>
       <c r="G9" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F10">
         <v>1.33</v>
       </c>
       <c r="G10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H10" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" t="s">
         <v>165</v>
       </c>
-      <c r="I10" t="s">
-        <v>170</v>
-      </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="2:12">
       <c r="B11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F11">
         <v>6.45</v>
       </c>
       <c r="G11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H11" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="L11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -26940,71 +28087,71 @@
   <sheetData>
     <row r="1" spans="1:23" s="56" customFormat="1" ht="22.15" customHeight="1">
       <c r="A1" s="53" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C1" s="54" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E1" s="54"/>
       <c r="F1" s="54" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H1" s="54" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I1" s="54" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J1" s="54"/>
       <c r="K1" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="L1" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="M1" s="54" t="s">
+        <v>220</v>
+      </c>
+      <c r="N1" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="O1" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="P1" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="L1" s="54" t="s">
+      <c r="Q1" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="M1" s="54" t="s">
+      <c r="R1" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="N1" s="54" t="s">
+      <c r="S1" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="O1" s="54" t="s">
+      <c r="T1" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="P1" s="54" t="s">
+      <c r="U1" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="Q1" s="54" t="s">
+      <c r="V1" s="55" t="s">
         <v>229</v>
-      </c>
-      <c r="R1" s="54" t="s">
-        <v>230</v>
-      </c>
-      <c r="S1" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="T1" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="U1" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="V1" s="55" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B2" s="58"/>
       <c r="C2" s="58"/>
@@ -27039,7 +28186,7 @@
     </row>
     <row r="3" spans="1:23" ht="27" customHeight="1" thickBot="1">
       <c r="A3" s="61" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B3" s="62">
         <v>2E-3</v>
@@ -27105,100 +28252,100 @@
         <v>2E-3</v>
       </c>
       <c r="W3" s="64" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86"/>
-      <c r="S4" s="86"/>
-      <c r="T4" s="86"/>
-      <c r="U4" s="86"/>
-      <c r="V4" s="87"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="90"/>
+      <c r="T4" s="90"/>
+      <c r="U4" s="90"/>
+      <c r="V4" s="91"/>
     </row>
     <row r="5" spans="1:23" s="56" customFormat="1" ht="18" customHeight="1">
       <c r="A5" s="65" t="s">
         <v>88</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E5" s="66"/>
       <c r="F5" s="66" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G5" s="66" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H5" s="66" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I5" s="66" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J5" s="66"/>
       <c r="K5" s="66" t="s">
+        <v>218</v>
+      </c>
+      <c r="L5" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>220</v>
+      </c>
+      <c r="N5" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="O5" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="P5" s="66" t="s">
         <v>223</v>
       </c>
-      <c r="L5" s="66" t="s">
+      <c r="Q5" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="M5" s="66" t="s">
+      <c r="R5" s="66" t="s">
         <v>225</v>
       </c>
-      <c r="N5" s="66" t="s">
+      <c r="S5" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="O5" s="66" t="s">
+      <c r="T5" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="P5" s="66" t="s">
+      <c r="U5" s="66" t="s">
         <v>228</v>
       </c>
-      <c r="Q5" s="66" t="s">
+      <c r="V5" s="67" t="s">
         <v>229</v>
-      </c>
-      <c r="R5" s="66" t="s">
-        <v>230</v>
-      </c>
-      <c r="S5" s="66" t="s">
-        <v>231</v>
-      </c>
-      <c r="T5" s="66" t="s">
-        <v>232</v>
-      </c>
-      <c r="U5" s="66" t="s">
-        <v>233</v>
-      </c>
-      <c r="V5" s="67" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="68" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B6" s="69"/>
       <c r="C6" s="69"/>
@@ -27237,7 +28384,7 @@
     </row>
     <row r="7" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A7" s="68" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B7" s="69"/>
       <c r="C7" s="69"/>
@@ -27275,7 +28422,7 @@
     </row>
     <row r="8" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A8" s="68" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B8" s="69"/>
       <c r="C8" s="69"/>
@@ -27313,7 +28460,7 @@
     </row>
     <row r="9" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A9" s="68" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B9" s="69"/>
       <c r="C9" s="69"/>
@@ -27351,7 +28498,7 @@
     </row>
     <row r="10" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A10" s="68" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B10" s="69"/>
       <c r="C10" s="69"/>
@@ -27389,7 +28536,7 @@
     </row>
     <row r="11" spans="1:23" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="A11" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B11" s="74"/>
       <c r="C11" s="74"/>
@@ -27426,54 +28573,54 @@
       <c r="V11" s="76"/>
     </row>
     <row r="12" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A12" s="85"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="86"/>
-      <c r="N12" s="86"/>
-      <c r="O12" s="86"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
-      <c r="S12" s="86"/>
-      <c r="T12" s="86"/>
-      <c r="U12" s="86"/>
-      <c r="V12" s="87"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="90"/>
+      <c r="N12" s="90"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="91"/>
     </row>
     <row r="13" spans="1:23" s="56" customFormat="1" ht="16.149999999999999" customHeight="1">
       <c r="A13" s="77" t="s">
         <v>88</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D13" s="78" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E13" s="78"/>
       <c r="F13" s="78" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G13" s="78" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H13" s="78" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I13" s="78" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78">
@@ -27515,7 +28662,7 @@
     </row>
     <row r="14" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="80" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
@@ -27547,7 +28694,7 @@
     </row>
     <row r="15" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="80" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
@@ -27579,7 +28726,7 @@
     </row>
     <row r="16" spans="1:23" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="80" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
@@ -27611,7 +28758,7 @@
     </row>
     <row r="17" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="80" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B17" s="59"/>
       <c r="C17" s="59"/>
@@ -27643,7 +28790,7 @@
     </row>
     <row r="18" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="80" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B18" s="59"/>
       <c r="C18" s="59"/>
@@ -27675,7 +28822,7 @@
     </row>
     <row r="19" spans="1:22" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="A19" s="81" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B19" s="82"/>
       <c r="C19" s="82"/>

--- a/月報/N/2025y LP-N 月報表格 - 複製.xlsx
+++ b/月報/N/2025y LP-N 月報表格 - 複製.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JYLIN\Desktop\gh\月報\N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B426C669-6D2B-430C-878B-134BEE5C42CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B9F88E-68BD-4D56-B91C-A94815AEC1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{2EF8ECB5-68E2-4B1C-8F0C-12438D926500}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{2EF8ECB5-68E2-4B1C-8F0C-12438D926500}"/>
   </bookViews>
   <sheets>
     <sheet name="2024 Poly PTC 統計" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="258">
   <si>
     <t>Target</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -914,6 +914,39 @@
   <si>
     <t>M/D%</t>
   </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>U/T%</t>
+  </si>
+  <si>
+    <t>L/T%</t>
+  </si>
+  <si>
+    <t>O/T%</t>
+  </si>
+  <si>
+    <t>MD+PM</t>
+  </si>
+  <si>
+    <t>P/M%</t>
+  </si>
+  <si>
+    <t>S/U%</t>
+  </si>
+  <si>
+    <t>F/D%</t>
+  </si>
+  <si>
+    <t>R/D%</t>
+  </si>
+  <si>
+    <t>P/D%</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
 </sst>
 </file>
 
@@ -4335,6 +4368,24 @@
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4375,6 +4426,24 @@
                 <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4415,6 +4484,24 @@
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4513,6 +4600,24 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4555,6 +4660,24 @@
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4655,6 +4778,24 @@
                 <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4753,6 +4894,24 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -19833,12 +19992,24 @@
       <c r="W3" s="7">
         <v>0</v>
       </c>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
+      <c r="X3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="2:36">
       <c r="B4" s="7" t="s">
@@ -19877,12 +20048,24 @@
       <c r="W4" s="7">
         <v>1</v>
       </c>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
+      <c r="X4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="2:36" ht="15.75">
       <c r="B5" s="7" t="s">
@@ -19921,12 +20104,24 @@
       <c r="W5" s="7">
         <v>0</v>
       </c>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
+      <c r="X5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>1</v>
+      </c>
       <c r="AJ5"/>
     </row>
     <row r="6" spans="2:36" ht="16.5">
@@ -19966,12 +20161,24 @@
       <c r="W6" s="7">
         <v>0</v>
       </c>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="7"/>
-      <c r="AC6" s="7"/>
+      <c r="X6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="7">
+        <v>0</v>
+      </c>
       <c r="AJ6" s="49"/>
     </row>
     <row r="7" spans="2:36">
@@ -20011,12 +20218,24 @@
       <c r="W7" s="7">
         <v>0</v>
       </c>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="7"/>
-      <c r="AC7" s="7"/>
+      <c r="X7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="2:36">
       <c r="B8" s="7" t="s">
@@ -20055,12 +20274,24 @@
       <c r="W8" s="7">
         <v>1</v>
       </c>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
+      <c r="X8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="2:36">
       <c r="B9" s="7" t="s">
@@ -20099,12 +20330,24 @@
       <c r="W9" s="7">
         <v>0</v>
       </c>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
+      <c r="X9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="2:36">
       <c r="B10" s="7" t="s">
@@ -20150,7 +20393,7 @@
         <v>2</v>
       </c>
       <c r="X10" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="X10" si="1">SUM(X3:X9)</f>
         <v>0</v>
       </c>
       <c r="Y10" s="7">
@@ -20171,7 +20414,7 @@
       </c>
       <c r="AC10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:36">
@@ -20211,12 +20454,24 @@
       <c r="W11" s="7">
         <v>318</v>
       </c>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
+      <c r="X11" s="7">
+        <v>421</v>
+      </c>
+      <c r="Y11" s="7">
+        <v>411</v>
+      </c>
+      <c r="Z11" s="7">
+        <v>160</v>
+      </c>
+      <c r="AA11" s="7">
+        <v>400</v>
+      </c>
+      <c r="AB11" s="7">
+        <v>429</v>
+      </c>
+      <c r="AC11" s="7">
+        <v>451</v>
+      </c>
     </row>
     <row r="12" spans="2:36">
       <c r="B12" s="7" t="s">
@@ -20889,7 +21144,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F36A1EE-6F84-497C-8595-7379F63D3470}">
-  <dimension ref="A2:AB158"/>
+  <dimension ref="A2:AB165"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -25202,7 +25457,89 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="79" spans="1:25">
+      <c r="N79" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25">
+      <c r="N80" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O80" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P80" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q80" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R80" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S80" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T80" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U80" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V80" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W80" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X80" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y80" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25">
+      <c r="N81" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O81" s="88">
+        <v>46.2</v>
+      </c>
+      <c r="P81" s="88">
+        <v>48.3</v>
+      </c>
+      <c r="Q81" s="88">
+        <v>0</v>
+      </c>
+      <c r="R81" s="51">
+        <f>SUM(O81:Q81)</f>
+        <v>94.5</v>
+      </c>
+      <c r="S81" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="T81" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="U81" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="V81" s="88">
+        <v>3.7</v>
+      </c>
+      <c r="W81" s="88">
+        <v>0</v>
+      </c>
+      <c r="X81" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25">
       <c r="A82" s="1" t="s">
         <v>59</v>
       </c>
@@ -25239,8 +25576,45 @@
       <c r="L82" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="83" spans="1:12">
+      <c r="N82" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O82" s="88">
+        <v>63.4</v>
+      </c>
+      <c r="P82" s="88">
+        <v>29.8</v>
+      </c>
+      <c r="Q82" s="88">
+        <v>0</v>
+      </c>
+      <c r="R82" s="51">
+        <f t="shared" ref="R82:R87" si="40">SUM(O82:Q82)</f>
+        <v>93.2</v>
+      </c>
+      <c r="S82" s="88">
+        <v>0</v>
+      </c>
+      <c r="T82" s="88">
+        <v>0</v>
+      </c>
+      <c r="U82" s="88">
+        <v>0</v>
+      </c>
+      <c r="V82" s="88">
+        <v>3.4</v>
+      </c>
+      <c r="W82" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="X82" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="88">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25">
       <c r="B83" s="7" t="s">
         <v>42</v>
       </c>
@@ -25275,8 +25649,45 @@
       <c r="L83" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:12">
+      <c r="N83" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O83" s="88">
+        <v>75.2</v>
+      </c>
+      <c r="P83" s="88">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="Q83" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="R83" s="51">
+        <f t="shared" si="40"/>
+        <v>93.699999999999989</v>
+      </c>
+      <c r="S83" s="88">
+        <v>3.9</v>
+      </c>
+      <c r="T83" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="U83" s="88">
+        <v>3.3</v>
+      </c>
+      <c r="V83" s="88">
+        <v>2.1</v>
+      </c>
+      <c r="W83" s="88">
+        <v>0</v>
+      </c>
+      <c r="X83" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25">
       <c r="B84" s="7" t="s">
         <v>41</v>
       </c>
@@ -25311,8 +25722,45 @@
       <c r="L84" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:12">
+      <c r="N84" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O84" s="88">
+        <v>60.9</v>
+      </c>
+      <c r="P84" s="88">
+        <v>32.4</v>
+      </c>
+      <c r="Q84" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="R84" s="51">
+        <f t="shared" si="40"/>
+        <v>94.2</v>
+      </c>
+      <c r="S84" s="88">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T84" s="88">
+        <v>0</v>
+      </c>
+      <c r="U84" s="88">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V84" s="88">
+        <v>3.4</v>
+      </c>
+      <c r="W84" s="88">
+        <v>0</v>
+      </c>
+      <c r="X84" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25">
       <c r="B85" s="7" t="s">
         <v>40</v>
       </c>
@@ -25347,8 +25795,45 @@
       <c r="L85" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:12">
+      <c r="N85" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O85" s="88">
+        <v>43.2</v>
+      </c>
+      <c r="P85" s="88">
+        <v>48.1</v>
+      </c>
+      <c r="Q85" s="88">
+        <v>2.8</v>
+      </c>
+      <c r="R85" s="51">
+        <f t="shared" si="40"/>
+        <v>94.100000000000009</v>
+      </c>
+      <c r="S85" s="88">
+        <v>3.3</v>
+      </c>
+      <c r="T85" s="88">
+        <v>0</v>
+      </c>
+      <c r="U85" s="88">
+        <v>3.3</v>
+      </c>
+      <c r="V85" s="88">
+        <v>2.4</v>
+      </c>
+      <c r="W85" s="88">
+        <v>0</v>
+      </c>
+      <c r="X85" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25">
       <c r="B86" s="7" t="s">
         <v>39</v>
       </c>
@@ -25383,8 +25868,45 @@
       <c r="L86" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:12">
+      <c r="N86" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O86" s="88">
+        <v>39.5</v>
+      </c>
+      <c r="P86" s="88">
+        <v>60.4</v>
+      </c>
+      <c r="Q86" s="88">
+        <v>0</v>
+      </c>
+      <c r="R86" s="51">
+        <f t="shared" si="40"/>
+        <v>99.9</v>
+      </c>
+      <c r="S86" s="88">
+        <v>0</v>
+      </c>
+      <c r="T86" s="88">
+        <v>0</v>
+      </c>
+      <c r="U86" s="88">
+        <v>0</v>
+      </c>
+      <c r="V86" s="88">
+        <v>0</v>
+      </c>
+      <c r="W86" s="88">
+        <v>0</v>
+      </c>
+      <c r="X86" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25">
       <c r="B87" s="7" t="s">
         <v>38</v>
       </c>
@@ -25419,8 +25941,45 @@
       <c r="L87" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:12">
+      <c r="N87" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O87" s="88">
+        <v>28.6</v>
+      </c>
+      <c r="P87" s="88">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="Q87" s="88">
+        <v>0</v>
+      </c>
+      <c r="R87" s="51">
+        <f t="shared" si="40"/>
+        <v>96.199999999999989</v>
+      </c>
+      <c r="S87" s="88">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T87" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="U87" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="V87" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="W87" s="88">
+        <v>0</v>
+      </c>
+      <c r="X87" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25">
       <c r="B88" s="7" t="s">
         <v>37</v>
       </c>
@@ -25438,31 +25997,111 @@
         <v>90.559999999999988</v>
       </c>
       <c r="G88" s="7">
-        <f t="shared" ref="G88:L88" si="40">AVERAGE(G83:G87)</f>
+        <f t="shared" ref="G88:L88" si="41">AVERAGE(G83:G87)</f>
         <v>4.7200000000000006</v>
       </c>
       <c r="H88" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="I88" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.06</v>
       </c>
       <c r="J88" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4.38</v>
       </c>
       <c r="K88" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L88" s="7">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="N88" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" s="88">
+        <v>51</v>
+      </c>
+      <c r="P88" s="88">
+        <v>43.5</v>
+      </c>
+      <c r="Q88" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="R88" s="88">
+        <f>AVERAGE(R81:R87)</f>
+        <v>95.114285714285714</v>
+      </c>
+      <c r="S88" s="88">
+        <v>1.9</v>
+      </c>
+      <c r="T88" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="U88" s="88">
+        <v>1.7</v>
+      </c>
+      <c r="V88" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W88" s="88">
+        <v>0</v>
+      </c>
+      <c r="X88" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="88">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25">
+      <c r="N90" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25">
+      <c r="N91" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O91" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P91" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q91" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R91" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S91" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T91" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U91" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V91" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W91" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X91" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y91" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25">
       <c r="A92" s="1" t="s">
         <v>58</v>
       </c>
@@ -25499,8 +26138,45 @@
       <c r="L92" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="93" spans="1:12">
+      <c r="N92" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O92" s="88">
+        <v>54.9</v>
+      </c>
+      <c r="P92" s="88">
+        <v>41.1</v>
+      </c>
+      <c r="Q92" s="88">
+        <v>0</v>
+      </c>
+      <c r="R92" s="51">
+        <f>SUM(O92:Q92)</f>
+        <v>96</v>
+      </c>
+      <c r="S92" s="88">
+        <v>2.9</v>
+      </c>
+      <c r="T92" s="88">
+        <v>2.9</v>
+      </c>
+      <c r="U92" s="88">
+        <v>0</v>
+      </c>
+      <c r="V92" s="88">
+        <v>1</v>
+      </c>
+      <c r="W92" s="88">
+        <v>0</v>
+      </c>
+      <c r="X92" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25">
       <c r="B93" s="7" t="s">
         <v>42</v>
       </c>
@@ -25535,8 +26211,45 @@
       <c r="L93" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:12">
+      <c r="N93" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O93" s="88">
+        <v>30</v>
+      </c>
+      <c r="P93" s="88">
+        <v>46.8</v>
+      </c>
+      <c r="Q93" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="R93" s="51">
+        <f t="shared" ref="R93:R98" si="42">SUM(O93:Q93)</f>
+        <v>77.3</v>
+      </c>
+      <c r="S93" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="T93" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="U93" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="V93" s="88">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="W93" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="X93" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="88">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25">
       <c r="B94" s="7" t="s">
         <v>41</v>
       </c>
@@ -25571,8 +26284,45 @@
       <c r="L94" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:12">
+      <c r="N94" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O94" s="88">
+        <v>62.9</v>
+      </c>
+      <c r="P94" s="88">
+        <v>28.1</v>
+      </c>
+      <c r="Q94" s="88">
+        <v>3.5</v>
+      </c>
+      <c r="R94" s="51">
+        <f t="shared" si="42"/>
+        <v>94.5</v>
+      </c>
+      <c r="S94" s="88">
+        <v>3.4</v>
+      </c>
+      <c r="T94" s="88">
+        <v>0</v>
+      </c>
+      <c r="U94" s="88">
+        <v>3.4</v>
+      </c>
+      <c r="V94" s="88">
+        <v>1.9</v>
+      </c>
+      <c r="W94" s="88">
+        <v>0</v>
+      </c>
+      <c r="X94" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25">
       <c r="B95" s="7" t="s">
         <v>40</v>
       </c>
@@ -25607,8 +26357,45 @@
       <c r="L95" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:12">
+      <c r="N95" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O95" s="88">
+        <v>62.3</v>
+      </c>
+      <c r="P95" s="88">
+        <v>31.8</v>
+      </c>
+      <c r="Q95" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="R95" s="51">
+        <f t="shared" si="42"/>
+        <v>94.399999999999991</v>
+      </c>
+      <c r="S95" s="88">
+        <v>3.4</v>
+      </c>
+      <c r="T95" s="88">
+        <v>0</v>
+      </c>
+      <c r="U95" s="88">
+        <v>3.4</v>
+      </c>
+      <c r="V95" s="88">
+        <v>1.9</v>
+      </c>
+      <c r="W95" s="88">
+        <v>0</v>
+      </c>
+      <c r="X95" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25">
       <c r="B96" s="7" t="s">
         <v>39</v>
       </c>
@@ -25643,8 +26430,45 @@
       <c r="L96" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:12">
+      <c r="N96" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O96" s="88">
+        <v>50.9</v>
+      </c>
+      <c r="P96" s="88">
+        <v>45.8</v>
+      </c>
+      <c r="Q96" s="88">
+        <v>1</v>
+      </c>
+      <c r="R96" s="51">
+        <f t="shared" si="42"/>
+        <v>97.699999999999989</v>
+      </c>
+      <c r="S96" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="T96" s="88">
+        <v>0</v>
+      </c>
+      <c r="U96" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="V96" s="88">
+        <v>0.8</v>
+      </c>
+      <c r="W96" s="88">
+        <v>0</v>
+      </c>
+      <c r="X96" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25">
       <c r="B97" s="7" t="s">
         <v>38</v>
       </c>
@@ -25679,53 +26503,171 @@
       <c r="L97" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:12">
+      <c r="N97" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O97" s="88">
+        <v>30</v>
+      </c>
+      <c r="P97" s="88">
+        <v>65.8</v>
+      </c>
+      <c r="Q97" s="88">
+        <v>0</v>
+      </c>
+      <c r="R97" s="51">
+        <f t="shared" si="42"/>
+        <v>95.8</v>
+      </c>
+      <c r="S97" s="88">
+        <v>0</v>
+      </c>
+      <c r="T97" s="88">
+        <v>0</v>
+      </c>
+      <c r="U97" s="88">
+        <v>0</v>
+      </c>
+      <c r="V97" s="88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W97" s="88">
+        <v>0</v>
+      </c>
+      <c r="X97" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25">
       <c r="B98" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C98" s="7">
-        <f t="shared" ref="C98:L98" si="41">AVERAGE(C93:C97)</f>
+        <f t="shared" ref="C98:L98" si="43">AVERAGE(C93:C97)</f>
         <v>79.040000000000006</v>
       </c>
       <c r="D98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="E98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>1.6</v>
       </c>
       <c r="F98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>89.44</v>
       </c>
       <c r="G98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>4.7799999999999994</v>
       </c>
       <c r="H98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.38</v>
       </c>
       <c r="J98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>4.9599999999999991</v>
       </c>
       <c r="K98" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.1</v>
       </c>
       <c r="L98" s="7">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N98" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O98" s="88">
+        <v>26</v>
+      </c>
+      <c r="P98" s="88">
+        <v>63.3</v>
+      </c>
+      <c r="Q98" s="88">
+        <v>0</v>
+      </c>
+      <c r="R98" s="51">
+        <f t="shared" si="42"/>
+        <v>89.3</v>
+      </c>
+      <c r="S98" s="88">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="T98" s="88">
+        <v>2.4</v>
+      </c>
+      <c r="U98" s="88">
+        <v>2.5</v>
+      </c>
+      <c r="V98" s="88">
+        <v>5.6</v>
+      </c>
+      <c r="W98" s="88">
+        <v>0</v>
+      </c>
+      <c r="X98" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25">
+      <c r="N99" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" s="88">
+        <v>45.3</v>
+      </c>
+      <c r="P99" s="88">
+        <v>46.1</v>
+      </c>
+      <c r="Q99" s="88">
+        <v>0.8</v>
+      </c>
+      <c r="R99" s="88">
+        <f>AVERAGE(R92:R98)</f>
+        <v>92.142857142857125</v>
+      </c>
+      <c r="S99" s="88">
+        <v>2.4</v>
+      </c>
+      <c r="T99" s="88">
+        <v>0.7</v>
+      </c>
+      <c r="U99" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="V99" s="88">
+        <v>3.5</v>
+      </c>
+      <c r="W99" s="88">
+        <v>0</v>
+      </c>
+      <c r="X99" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="88">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25">
+      <c r="N101" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25">
       <c r="A102" s="1" t="s">
         <v>57</v>
       </c>
@@ -25762,8 +26704,44 @@
       <c r="L102" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="103" spans="1:12">
+      <c r="N102" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O102" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P102" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q102" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R102" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S102" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T102" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U102" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V102" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W102" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X102" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y102" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25">
       <c r="B103" s="7" t="s">
         <v>42</v>
       </c>
@@ -25798,8 +26776,45 @@
       <c r="L103" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:12">
+      <c r="N103" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O103" s="88">
+        <v>33.6</v>
+      </c>
+      <c r="P103" s="88">
+        <v>57.6</v>
+      </c>
+      <c r="Q103" s="88">
+        <v>0</v>
+      </c>
+      <c r="R103" s="51">
+        <f>SUM(O103:Q103)</f>
+        <v>91.2</v>
+      </c>
+      <c r="S103" s="88">
+        <v>3</v>
+      </c>
+      <c r="T103" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="U103" s="88">
+        <v>2.8</v>
+      </c>
+      <c r="V103" s="88">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W103" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="X103" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25">
       <c r="B104" s="7" t="s">
         <v>41</v>
       </c>
@@ -25834,8 +26849,45 @@
       <c r="L104" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:12">
+      <c r="N104" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O104" s="88">
+        <v>52.4</v>
+      </c>
+      <c r="P104" s="88">
+        <v>39.6</v>
+      </c>
+      <c r="Q104" s="88">
+        <v>0</v>
+      </c>
+      <c r="R104" s="51">
+        <f t="shared" ref="R104:R109" si="44">SUM(O104:Q104)</f>
+        <v>92</v>
+      </c>
+      <c r="S104" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="T104" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="U104" s="88">
+        <v>0</v>
+      </c>
+      <c r="V104" s="88">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="W104" s="88">
+        <v>0</v>
+      </c>
+      <c r="X104" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25">
       <c r="B105" s="7" t="s">
         <v>40</v>
       </c>
@@ -25870,8 +26922,45 @@
       <c r="L105" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:12">
+      <c r="N105" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O105" s="88">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="P105" s="88">
+        <v>22.9</v>
+      </c>
+      <c r="Q105" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="R105" s="51">
+        <f t="shared" si="44"/>
+        <v>91.8</v>
+      </c>
+      <c r="S105" s="88">
+        <v>3.9</v>
+      </c>
+      <c r="T105" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="U105" s="88">
+        <v>3.7</v>
+      </c>
+      <c r="V105" s="88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W105" s="88">
+        <v>0</v>
+      </c>
+      <c r="X105" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25">
       <c r="B106" s="7" t="s">
         <v>39</v>
       </c>
@@ -25906,8 +26995,45 @@
       <c r="L106" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:12">
+      <c r="N106" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O106" s="88">
+        <v>58.7</v>
+      </c>
+      <c r="P106" s="88">
+        <v>38</v>
+      </c>
+      <c r="Q106" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="R106" s="51">
+        <f t="shared" si="44"/>
+        <v>97.600000000000009</v>
+      </c>
+      <c r="S106" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="T106" s="88">
+        <v>0</v>
+      </c>
+      <c r="U106" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="V106" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="W106" s="88">
+        <v>0</v>
+      </c>
+      <c r="X106" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25">
       <c r="B107" s="7" t="s">
         <v>38</v>
       </c>
@@ -25942,53 +27068,205 @@
       <c r="L107" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:12">
+      <c r="N107" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O107" s="88">
+        <v>34</v>
+      </c>
+      <c r="P107" s="88">
+        <v>59.3</v>
+      </c>
+      <c r="Q107" s="88">
+        <v>0</v>
+      </c>
+      <c r="R107" s="51">
+        <f t="shared" si="44"/>
+        <v>93.3</v>
+      </c>
+      <c r="S107" s="88">
+        <v>4.7</v>
+      </c>
+      <c r="T107" s="88">
+        <v>0</v>
+      </c>
+      <c r="U107" s="88">
+        <v>4.7</v>
+      </c>
+      <c r="V107" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="W107" s="88">
+        <v>0</v>
+      </c>
+      <c r="X107" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25">
       <c r="B108" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C108" s="7">
-        <f t="shared" ref="C108:L108" si="42">AVERAGE(C103:C107)</f>
+        <f t="shared" ref="C108:L108" si="45">AVERAGE(C103:C107)</f>
         <v>70.84</v>
       </c>
       <c r="D108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>17.34</v>
       </c>
       <c r="E108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>2.62</v>
       </c>
       <c r="F108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>90.8</v>
       </c>
       <c r="G108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="H108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="I108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="J108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>3.7</v>
       </c>
       <c r="K108" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L108" s="7">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="N108" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O108" s="88">
+        <v>35.4</v>
+      </c>
+      <c r="P108" s="88">
+        <v>61.3</v>
+      </c>
+      <c r="Q108" s="88">
+        <v>0</v>
+      </c>
+      <c r="R108" s="51">
+        <f t="shared" si="44"/>
+        <v>96.699999999999989</v>
+      </c>
+      <c r="S108" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="T108" s="88">
+        <v>0</v>
+      </c>
+      <c r="U108" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="V108" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="W108" s="88">
+        <v>0</v>
+      </c>
+      <c r="X108" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25">
+      <c r="N109" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O109" s="88">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="P109" s="88">
+        <v>79.8</v>
+      </c>
+      <c r="Q109" s="88">
+        <v>0</v>
+      </c>
+      <c r="R109" s="51">
+        <f t="shared" si="44"/>
+        <v>99.9</v>
+      </c>
+      <c r="S109" s="88">
+        <v>0</v>
+      </c>
+      <c r="T109" s="88">
+        <v>0</v>
+      </c>
+      <c r="U109" s="88">
+        <v>0</v>
+      </c>
+      <c r="V109" s="88">
+        <v>0</v>
+      </c>
+      <c r="W109" s="88">
+        <v>0</v>
+      </c>
+      <c r="X109" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25">
+      <c r="N110" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O110" s="88">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="P110" s="88">
+        <v>56.9</v>
+      </c>
+      <c r="Q110" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="R110" s="88">
+        <f>AVERAGE(R103:R109)</f>
+        <v>94.642857142857139</v>
+      </c>
+      <c r="S110" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="T110" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="U110" s="88">
+        <v>1.5</v>
+      </c>
+      <c r="V110" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="W110" s="88">
+        <v>0</v>
+      </c>
+      <c r="X110" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -26025,8 +27303,11 @@
       <c r="L112" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="113" spans="1:17">
+      <c r="N112" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28">
       <c r="B113" s="7" t="s">
         <v>42</v>
       </c>
@@ -26061,8 +27342,44 @@
       <c r="L113" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:17">
+      <c r="N113" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O113" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P113" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q113" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R113" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S113" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T113" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U113" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V113" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W113" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X113" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y113" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28">
       <c r="B114" s="7" t="s">
         <v>41</v>
       </c>
@@ -26097,8 +27414,55 @@
       <c r="L114" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:17">
+      <c r="N114" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O114" s="88">
+        <f>AVERAGE(O103,O92,O81)</f>
+        <v>44.9</v>
+      </c>
+      <c r="P114" s="88">
+        <f t="shared" ref="P114:S114" si="46">AVERAGE(P103,P92,P81)</f>
+        <v>49</v>
+      </c>
+      <c r="Q114" s="88">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="R114" s="51">
+        <f>SUM(O114:Q114)</f>
+        <v>93.9</v>
+      </c>
+      <c r="S114" s="88">
+        <f t="shared" si="46"/>
+        <v>2.5</v>
+      </c>
+      <c r="T114" s="88">
+        <f t="shared" ref="T114:Y114" si="47">AVERAGE(T103,T92,T81)</f>
+        <v>1.1333333333333333</v>
+      </c>
+      <c r="U114" s="88">
+        <f t="shared" si="47"/>
+        <v>1.3666666666666665</v>
+      </c>
+      <c r="V114" s="88">
+        <f t="shared" si="47"/>
+        <v>3.2000000000000006</v>
+      </c>
+      <c r="W114" s="88">
+        <f t="shared" si="47"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="X114" s="88">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="Y114" s="88">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28">
       <c r="B115" s="7" t="s">
         <v>40</v>
       </c>
@@ -26133,8 +27497,55 @@
       <c r="L115" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:17">
+      <c r="N115" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O115" s="88">
+        <f t="shared" ref="O115:Q120" si="48">AVERAGE(O104,O93,O82)</f>
+        <v>48.6</v>
+      </c>
+      <c r="P115" s="88">
+        <f t="shared" si="48"/>
+        <v>38.733333333333334</v>
+      </c>
+      <c r="Q115" s="88">
+        <f t="shared" si="48"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="R115" s="51">
+        <f t="shared" ref="R115:R120" si="49">SUM(O115:Q115)</f>
+        <v>87.500000000000014</v>
+      </c>
+      <c r="S115" s="88">
+        <f t="shared" ref="S115:Y115" si="50">AVERAGE(S104,S93,S82)</f>
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="T115" s="88">
+        <f t="shared" si="50"/>
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="U115" s="88">
+        <f t="shared" si="50"/>
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="V115" s="88">
+        <f t="shared" si="50"/>
+        <v>5.7666666666666666</v>
+      </c>
+      <c r="W115" s="88">
+        <f t="shared" si="50"/>
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="X115" s="88">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Y115" s="88">
+        <f t="shared" si="50"/>
+        <v>5.3666666666666671</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28">
       <c r="B116" s="7" t="s">
         <v>39</v>
       </c>
@@ -26169,8 +27580,55 @@
       <c r="L116" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:17">
+      <c r="N116" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O116" s="88">
+        <f t="shared" si="48"/>
+        <v>68.399999999999991</v>
+      </c>
+      <c r="P116" s="88">
+        <f t="shared" si="48"/>
+        <v>22.966666666666669</v>
+      </c>
+      <c r="Q116" s="88">
+        <f t="shared" si="48"/>
+        <v>1.9666666666666666</v>
+      </c>
+      <c r="R116" s="51">
+        <f t="shared" si="49"/>
+        <v>93.333333333333329</v>
+      </c>
+      <c r="S116" s="88">
+        <f t="shared" ref="S116:Y116" si="51">AVERAGE(S105,S94,S83)</f>
+        <v>3.7333333333333329</v>
+      </c>
+      <c r="T116" s="88">
+        <f t="shared" si="51"/>
+        <v>0.23333333333333331</v>
+      </c>
+      <c r="U116" s="88">
+        <f t="shared" si="51"/>
+        <v>3.4666666666666663</v>
+      </c>
+      <c r="V116" s="88">
+        <f t="shared" si="51"/>
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="W116" s="88">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="X116" s="88">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="Y116" s="88">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28">
       <c r="B117" s="7" t="s">
         <v>38</v>
       </c>
@@ -26205,53 +27663,294 @@
       <c r="L117" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:17">
+      <c r="N117" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O117" s="88">
+        <f t="shared" si="48"/>
+        <v>60.633333333333333</v>
+      </c>
+      <c r="P117" s="88">
+        <f t="shared" si="48"/>
+        <v>34.066666666666663</v>
+      </c>
+      <c r="Q117" s="88">
+        <f t="shared" si="48"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="R117" s="51">
+        <f t="shared" si="49"/>
+        <v>95.399999999999991</v>
+      </c>
+      <c r="S117" s="88">
+        <f t="shared" ref="S117:Y117" si="52">AVERAGE(S106,S95,S84)</f>
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="T117" s="88">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="U117" s="88">
+        <f t="shared" si="52"/>
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="V117" s="88">
+        <f t="shared" si="52"/>
+        <v>2.0666666666666664</v>
+      </c>
+      <c r="W117" s="88">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="X117" s="88">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Y117" s="88">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28">
       <c r="B118" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C118" s="7">
-        <f t="shared" ref="C118:L118" si="43">AVERAGE(C113:C117)</f>
+        <f t="shared" ref="C118:L118" si="53">AVERAGE(C113:C117)</f>
         <v>73.539999999999992</v>
       </c>
       <c r="D118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>13.6</v>
       </c>
       <c r="E118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>2.7800000000000002</v>
       </c>
       <c r="F118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>89.919999999999987</v>
       </c>
       <c r="G118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>5.22</v>
       </c>
       <c r="H118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0.27999999999999997</v>
       </c>
       <c r="J118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>4.2600000000000007</v>
       </c>
       <c r="K118" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L118" s="7">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="N118" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O118" s="88">
+        <f t="shared" si="48"/>
+        <v>42.70000000000001</v>
+      </c>
+      <c r="P118" s="88">
+        <f t="shared" si="48"/>
+        <v>51.066666666666663</v>
+      </c>
+      <c r="Q118" s="88">
+        <f>AVERAGE(Q107,Q96,Q85)</f>
+        <v>1.2666666666666666</v>
+      </c>
+      <c r="R118" s="51">
+        <f t="shared" si="49"/>
+        <v>95.033333333333346</v>
+      </c>
+      <c r="S118" s="88">
+        <f t="shared" ref="S118:Y118" si="54">AVERAGE(S107,S96,S85)</f>
+        <v>3.0666666666666664</v>
+      </c>
+      <c r="T118" s="88">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U118" s="88">
+        <f t="shared" si="54"/>
+        <v>3.0666666666666664</v>
+      </c>
+      <c r="V118" s="88">
+        <f t="shared" si="54"/>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="W118" s="88">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="X118" s="88">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="Y118" s="88">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28">
+      <c r="N119" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O119" s="88">
+        <f t="shared" si="48"/>
+        <v>34.966666666666669</v>
+      </c>
+      <c r="P119" s="88">
+        <f t="shared" si="48"/>
+        <v>62.5</v>
+      </c>
+      <c r="Q119" s="88">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="R119" s="51">
+        <f t="shared" si="49"/>
+        <v>97.466666666666669</v>
+      </c>
+      <c r="S119" s="88">
+        <f t="shared" ref="S119:Y119" si="55">AVERAGE(S108,S97,S86)</f>
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="T119" s="88">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="U119" s="88">
+        <f t="shared" si="55"/>
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="V119" s="88">
+        <f t="shared" si="55"/>
+        <v>1.9666666666666666</v>
+      </c>
+      <c r="W119" s="88">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="X119" s="88">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="Y119" s="88">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28">
+      <c r="N120" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O120" s="88">
+        <f t="shared" si="48"/>
+        <v>24.900000000000002</v>
+      </c>
+      <c r="P120" s="88">
+        <f t="shared" si="48"/>
+        <v>70.233333333333334</v>
+      </c>
+      <c r="Q120" s="88">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="R120" s="51">
+        <f t="shared" si="49"/>
+        <v>95.13333333333334</v>
+      </c>
+      <c r="S120" s="88">
+        <f t="shared" ref="S120:Y120" si="56">AVERAGE(S109,S98,S87)</f>
+        <v>2.3666666666666667</v>
+      </c>
+      <c r="T120" s="88">
+        <f t="shared" si="56"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="U120" s="88">
+        <f t="shared" si="56"/>
+        <v>1.4333333333333333</v>
+      </c>
+      <c r="V120" s="88">
+        <f t="shared" si="56"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="W120" s="88">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="X120" s="88">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="Y120" s="88">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28">
+      <c r="N121" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O121" s="88">
+        <f>AVERAGE(O114:O120)</f>
+        <v>46.442857142857129</v>
+      </c>
+      <c r="P121" s="88">
+        <f t="shared" ref="P121:Y121" si="57">AVERAGE(P114:P120)</f>
+        <v>46.938095238095237</v>
+      </c>
+      <c r="Q121" s="88">
+        <f t="shared" si="57"/>
+        <v>0.58571428571428563</v>
+      </c>
+      <c r="R121" s="88">
+        <f t="shared" si="57"/>
+        <v>93.966666666666669</v>
+      </c>
+      <c r="S121" s="88">
+        <f t="shared" si="57"/>
+        <v>2.1571428571428575</v>
+      </c>
+      <c r="T121" s="88">
+        <f t="shared" si="57"/>
+        <v>0.37619047619047619</v>
+      </c>
+      <c r="U121" s="88">
+        <f t="shared" si="57"/>
+        <v>1.7714285714285711</v>
+      </c>
+      <c r="V121" s="88">
+        <f t="shared" si="57"/>
+        <v>2.8142857142857136</v>
+      </c>
+      <c r="W121" s="88">
+        <f t="shared" si="57"/>
+        <v>8.0952380952380956E-2</v>
+      </c>
+      <c r="X121" s="88">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="Y121" s="88">
+        <f t="shared" si="57"/>
+        <v>0.76666666666666672</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28">
       <c r="A122" s="1" t="s">
         <v>56</v>
       </c>
@@ -26289,7 +27988,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="123" spans="1:17">
+    <row r="123" spans="1:28" ht="15">
       <c r="B123" s="7" t="s">
         <v>42</v>
       </c>
@@ -26324,8 +28023,14 @@
       <c r="L123" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:17">
+      <c r="N123" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z123" s="1"/>
+      <c r="AA123" s="1"/>
+      <c r="AB123" s="1"/>
+    </row>
+    <row r="124" spans="1:28" ht="15">
       <c r="B124" s="7" t="s">
         <v>41</v>
       </c>
@@ -26360,8 +28065,47 @@
       <c r="L124" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:17">
+      <c r="N124" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O124" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="P124" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q124" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="R124" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S124" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="T124" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U124" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="V124" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="W124" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="X124" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y124" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z124" s="1"/>
+      <c r="AA124" s="1"/>
+      <c r="AB124" s="1"/>
+    </row>
+    <row r="125" spans="1:28" ht="15">
       <c r="B125" s="7" t="s">
         <v>40</v>
       </c>
@@ -26396,8 +28140,48 @@
       <c r="L125" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:17">
+      <c r="N125" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O125" s="88">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="P125" s="88">
+        <v>59.3</v>
+      </c>
+      <c r="Q125" s="88">
+        <v>0</v>
+      </c>
+      <c r="R125" s="51">
+        <f>SUM(O125:Q125)</f>
+        <v>91.5</v>
+      </c>
+      <c r="S125" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="T125" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="U125" s="88">
+        <v>0</v>
+      </c>
+      <c r="V125" s="88">
+        <v>6.4</v>
+      </c>
+      <c r="W125" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="X125" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y125" s="88">
+        <v>0</v>
+      </c>
+      <c r="Z125" s="1"/>
+      <c r="AA125" s="1"/>
+      <c r="AB125" s="1"/>
+    </row>
+    <row r="126" spans="1:28" ht="15">
       <c r="B126" s="7" t="s">
         <v>39</v>
       </c>
@@ -26432,8 +28216,48 @@
       <c r="L126" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:17">
+      <c r="N126" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O126" s="88">
+        <v>50.9</v>
+      </c>
+      <c r="P126" s="88">
+        <v>32.5</v>
+      </c>
+      <c r="Q126" s="88">
+        <v>0</v>
+      </c>
+      <c r="R126" s="51">
+        <f t="shared" ref="R126:R131" si="58">SUM(O126:Q126)</f>
+        <v>83.4</v>
+      </c>
+      <c r="S126" s="88">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T126" s="88">
+        <v>1.9</v>
+      </c>
+      <c r="U126" s="88">
+        <v>2.6</v>
+      </c>
+      <c r="V126" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W126" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="X126" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="88">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Z126" s="1"/>
+      <c r="AA126" s="1"/>
+      <c r="AB126" s="1"/>
+    </row>
+    <row r="127" spans="1:28" ht="15">
       <c r="B127" s="7" t="s">
         <v>38</v>
       </c>
@@ -26468,74 +28292,259 @@
       <c r="L127" s="7">
         <v>0</v>
       </c>
-      <c r="Q127" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17">
+      <c r="N127" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O127" s="88">
+        <v>61.5</v>
+      </c>
+      <c r="P127" s="88">
+        <v>32.4</v>
+      </c>
+      <c r="Q127" s="88">
+        <v>0</v>
+      </c>
+      <c r="R127" s="51">
+        <f t="shared" si="58"/>
+        <v>93.9</v>
+      </c>
+      <c r="S127" s="88">
+        <v>3.6</v>
+      </c>
+      <c r="T127" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="U127" s="88">
+        <v>3</v>
+      </c>
+      <c r="V127" s="88">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W127" s="88">
+        <v>0</v>
+      </c>
+      <c r="X127" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y127" s="88">
+        <v>0</v>
+      </c>
+      <c r="Z127" s="1"/>
+      <c r="AA127" s="1"/>
+      <c r="AB127" s="1"/>
+    </row>
+    <row r="128" spans="1:28" ht="15">
       <c r="B128" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C128" s="7">
-        <f t="shared" ref="C128:L128" si="44">AVERAGE(C123:C127)</f>
+        <f t="shared" ref="C128:L128" si="59">AVERAGE(C123:C127)</f>
         <v>68.960000000000008</v>
       </c>
       <c r="D128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>16.28</v>
       </c>
       <c r="E128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>3.16</v>
       </c>
       <c r="F128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>88.4</v>
       </c>
       <c r="G128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>6.7200000000000006</v>
       </c>
       <c r="H128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>0.1</v>
       </c>
       <c r="I128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="J128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>4.28</v>
       </c>
       <c r="K128" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="L128" s="7">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="Q128" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17">
-      <c r="Q129" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17">
-      <c r="Q130" s="1">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="N128" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O128" s="88">
+        <v>57.5</v>
+      </c>
+      <c r="P128" s="88">
+        <v>32.5</v>
+      </c>
+      <c r="Q128" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="R128" s="51">
+        <f t="shared" si="58"/>
+        <v>91.4</v>
+      </c>
+      <c r="S128" s="88">
+        <v>5.8</v>
+      </c>
+      <c r="T128" s="88">
+        <v>0.7</v>
+      </c>
+      <c r="U128" s="88">
+        <v>5</v>
+      </c>
+      <c r="V128" s="88">
+        <v>2.6</v>
+      </c>
+      <c r="W128" s="88">
+        <v>0</v>
+      </c>
+      <c r="X128" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y128" s="88">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="1"/>
+      <c r="AA128" s="1"/>
+      <c r="AB128" s="1"/>
+    </row>
+    <row r="129" spans="1:28" ht="15">
+      <c r="N129" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O129" s="88">
+        <v>43.3</v>
+      </c>
+      <c r="P129" s="88">
+        <v>50.8</v>
+      </c>
+      <c r="Q129" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="R129" s="51">
+        <f t="shared" si="58"/>
+        <v>95.699999999999989</v>
+      </c>
+      <c r="S129" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T129" s="88">
+        <v>1.3</v>
+      </c>
+      <c r="U129" s="88">
+        <v>1</v>
+      </c>
+      <c r="V129" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="W129" s="88">
+        <v>0</v>
+      </c>
+      <c r="X129" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y129" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="Z129" s="1"/>
+      <c r="AA129" s="1"/>
+      <c r="AB129" s="1"/>
+    </row>
+    <row r="130" spans="1:28" ht="15">
+      <c r="N130" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O130" s="88">
+        <v>25.5</v>
+      </c>
+      <c r="P130" s="88">
+        <v>73.7</v>
+      </c>
+      <c r="Q130" s="88">
+        <v>0</v>
+      </c>
+      <c r="R130" s="51">
+        <f t="shared" si="58"/>
+        <v>99.2</v>
+      </c>
+      <c r="S130" s="88">
+        <v>0.4</v>
+      </c>
+      <c r="T130" s="88">
+        <v>0.4</v>
+      </c>
+      <c r="U130" s="88">
+        <v>0</v>
+      </c>
+      <c r="V130" s="88">
+        <v>0</v>
+      </c>
+      <c r="W130" s="88">
+        <v>0</v>
+      </c>
+      <c r="X130" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="88">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="131" spans="1:17">
-      <c r="Q131" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17">
+      <c r="Z130" s="1"/>
+      <c r="AA130" s="1"/>
+      <c r="AB130" s="1"/>
+    </row>
+    <row r="131" spans="1:28" ht="15">
+      <c r="N131" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O131" s="88">
+        <v>29</v>
+      </c>
+      <c r="P131" s="88">
+        <v>59.5</v>
+      </c>
+      <c r="Q131" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="R131" s="51">
+        <f t="shared" si="58"/>
+        <v>89.7</v>
+      </c>
+      <c r="S131" s="88">
+        <v>8.6</v>
+      </c>
+      <c r="T131" s="88">
+        <v>0</v>
+      </c>
+      <c r="U131" s="88">
+        <v>8.6</v>
+      </c>
+      <c r="V131" s="88">
+        <v>1.5</v>
+      </c>
+      <c r="W131" s="88">
+        <v>0</v>
+      </c>
+      <c r="X131" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="88">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="1"/>
+      <c r="AA131" s="1"/>
+      <c r="AB131" s="1"/>
+    </row>
+    <row r="132" spans="1:28" ht="15">
       <c r="A132" s="1" t="s">
         <v>55</v>
       </c>
@@ -26572,8 +28581,48 @@
       <c r="L132" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="133" spans="1:17">
+      <c r="N132" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O132" s="88">
+        <v>42.8</v>
+      </c>
+      <c r="P132" s="88">
+        <v>48.7</v>
+      </c>
+      <c r="Q132" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="R132" s="88">
+        <f t="shared" ref="R132" si="60">AVERAGE(R125:R131)</f>
+        <v>92.114285714285728</v>
+      </c>
+      <c r="S132" s="88">
+        <v>3.8</v>
+      </c>
+      <c r="T132" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="U132" s="88">
+        <v>2.9</v>
+      </c>
+      <c r="V132" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W132" s="88">
+        <v>0</v>
+      </c>
+      <c r="X132" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="Z132" s="1"/>
+      <c r="AA132" s="1"/>
+      <c r="AB132" s="1"/>
+    </row>
+    <row r="133" spans="1:28">
       <c r="B133" s="7" t="s">
         <v>42</v>
       </c>
@@ -26608,8 +28657,14 @@
       <c r="L133" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:17">
+      <c r="N133"/>
+      <c r="O133"/>
+      <c r="S133" s="1"/>
+      <c r="Z133" s="1"/>
+      <c r="AA133" s="1"/>
+      <c r="AB133" s="1"/>
+    </row>
+    <row r="134" spans="1:28" ht="15">
       <c r="B134" s="7" t="s">
         <v>41</v>
       </c>
@@ -26644,8 +28699,14 @@
       <c r="L134" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:17">
+      <c r="N134" s="1">
+        <v>11</v>
+      </c>
+      <c r="Z134" s="1"/>
+      <c r="AA134" s="1"/>
+      <c r="AB134" s="1"/>
+    </row>
+    <row r="135" spans="1:28" ht="15">
       <c r="B135" s="7" t="s">
         <v>40</v>
       </c>
@@ -26680,8 +28741,47 @@
       <c r="L135" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:17">
+      <c r="N135" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O135" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="P135" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q135" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="R135" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S135" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="T135" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U135" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="V135" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="W135" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="X135" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y135" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z135" s="1"/>
+      <c r="AA135" s="1"/>
+      <c r="AB135" s="1"/>
+    </row>
+    <row r="136" spans="1:28">
       <c r="B136" s="7" t="s">
         <v>39</v>
       </c>
@@ -26716,8 +28816,45 @@
       <c r="L136" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:17">
+      <c r="N136" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O136" s="88">
+        <v>48.3</v>
+      </c>
+      <c r="P136" s="88">
+        <v>51.6</v>
+      </c>
+      <c r="Q136" s="88">
+        <v>0</v>
+      </c>
+      <c r="R136" s="51">
+        <f>SUM(O136:Q136)</f>
+        <v>99.9</v>
+      </c>
+      <c r="S136" s="88">
+        <v>0</v>
+      </c>
+      <c r="T136" s="88">
+        <v>0</v>
+      </c>
+      <c r="U136" s="88">
+        <v>0</v>
+      </c>
+      <c r="V136" s="88">
+        <v>0</v>
+      </c>
+      <c r="W136" s="88">
+        <v>0</v>
+      </c>
+      <c r="X136" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:28">
       <c r="B137" s="7" t="s">
         <v>38</v>
       </c>
@@ -26752,53 +28889,244 @@
       <c r="L137" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:17">
+      <c r="N137" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O137" s="88">
+        <v>48.2</v>
+      </c>
+      <c r="P137" s="88">
+        <v>51.7</v>
+      </c>
+      <c r="Q137" s="88">
+        <v>0</v>
+      </c>
+      <c r="R137" s="51">
+        <f t="shared" ref="R137:R142" si="61">SUM(O137:Q137)</f>
+        <v>99.9</v>
+      </c>
+      <c r="S137" s="88">
+        <v>0</v>
+      </c>
+      <c r="T137" s="88">
+        <v>0</v>
+      </c>
+      <c r="U137" s="88">
+        <v>0</v>
+      </c>
+      <c r="V137" s="88">
+        <v>0</v>
+      </c>
+      <c r="W137" s="88">
+        <v>0</v>
+      </c>
+      <c r="X137" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:28">
       <c r="B138" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C138" s="7">
-        <f t="shared" ref="C138:L138" si="45">AVERAGE(C133:C137)</f>
+        <f t="shared" ref="C138:L138" si="62">AVERAGE(C133:C137)</f>
         <v>79.22</v>
       </c>
       <c r="D138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>7.6199999999999992</v>
       </c>
       <c r="E138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>2.68</v>
       </c>
       <c r="F138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>89.52</v>
       </c>
       <c r="G138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>6.02</v>
       </c>
       <c r="H138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="I138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>0.42000000000000004</v>
       </c>
       <c r="J138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>3.7600000000000002</v>
       </c>
       <c r="K138" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="L138" s="7">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N138" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O138" s="88">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="P138" s="88">
+        <v>22.3</v>
+      </c>
+      <c r="Q138" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="R138" s="51">
+        <f t="shared" si="61"/>
+        <v>93.100000000000009</v>
+      </c>
+      <c r="S138" s="88">
+        <v>4</v>
+      </c>
+      <c r="T138" s="88">
+        <v>0</v>
+      </c>
+      <c r="U138" s="88">
+        <v>4</v>
+      </c>
+      <c r="V138" s="88">
+        <v>2.7</v>
+      </c>
+      <c r="W138" s="88">
+        <v>0</v>
+      </c>
+      <c r="X138" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:28">
+      <c r="N139" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O139" s="88">
+        <v>67</v>
+      </c>
+      <c r="P139" s="88">
+        <v>22.5</v>
+      </c>
+      <c r="Q139" s="88">
+        <v>0.7</v>
+      </c>
+      <c r="R139" s="51">
+        <f t="shared" si="61"/>
+        <v>90.2</v>
+      </c>
+      <c r="S139" s="88">
+        <v>6.9</v>
+      </c>
+      <c r="T139" s="88">
+        <v>0</v>
+      </c>
+      <c r="U139" s="88">
+        <v>6.9</v>
+      </c>
+      <c r="V139" s="88">
+        <v>2.7</v>
+      </c>
+      <c r="W139" s="88">
+        <v>0</v>
+      </c>
+      <c r="X139" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:28">
+      <c r="N140" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O140" s="88">
+        <v>56.9</v>
+      </c>
+      <c r="P140" s="88">
+        <v>33</v>
+      </c>
+      <c r="Q140" s="88">
+        <v>0</v>
+      </c>
+      <c r="R140" s="51">
+        <f t="shared" si="61"/>
+        <v>89.9</v>
+      </c>
+      <c r="S140" s="88">
+        <v>6.4</v>
+      </c>
+      <c r="T140" s="88">
+        <v>2.9</v>
+      </c>
+      <c r="U140" s="88">
+        <v>3.5</v>
+      </c>
+      <c r="V140" s="88">
+        <v>3.5</v>
+      </c>
+      <c r="W140" s="88">
+        <v>0</v>
+      </c>
+      <c r="X140" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y140" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:28">
+      <c r="N141" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O141" s="88">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="P141" s="88">
+        <v>81.5</v>
+      </c>
+      <c r="Q141" s="88">
+        <v>0</v>
+      </c>
+      <c r="R141" s="51">
+        <f t="shared" si="61"/>
+        <v>99.9</v>
+      </c>
+      <c r="S141" s="88">
+        <v>0</v>
+      </c>
+      <c r="T141" s="88">
+        <v>0</v>
+      </c>
+      <c r="U141" s="88">
+        <v>0</v>
+      </c>
+      <c r="V141" s="88">
+        <v>0</v>
+      </c>
+      <c r="W141" s="88">
+        <v>0</v>
+      </c>
+      <c r="X141" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:28">
       <c r="A142" s="1" t="s">
         <v>54</v>
       </c>
@@ -26835,8 +29163,45 @@
       <c r="L142" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="143" spans="1:17">
+      <c r="N142" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O142" s="88">
+        <v>31.4</v>
+      </c>
+      <c r="P142" s="88">
+        <v>41.7</v>
+      </c>
+      <c r="Q142" s="88">
+        <v>0</v>
+      </c>
+      <c r="R142" s="51">
+        <f t="shared" si="61"/>
+        <v>73.099999999999994</v>
+      </c>
+      <c r="S142" s="88">
+        <v>10.5</v>
+      </c>
+      <c r="T142" s="88">
+        <v>0</v>
+      </c>
+      <c r="U142" s="88">
+        <v>10.5</v>
+      </c>
+      <c r="V142" s="88">
+        <v>0.7</v>
+      </c>
+      <c r="W142" s="88">
+        <v>0</v>
+      </c>
+      <c r="X142" s="88">
+        <v>15.5</v>
+      </c>
+      <c r="Y142" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:28">
       <c r="B143" s="7" t="s">
         <v>42</v>
       </c>
@@ -26871,8 +29236,45 @@
       <c r="L143" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:17">
+      <c r="N143" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O143" s="88">
+        <v>48.6</v>
+      </c>
+      <c r="P143" s="88">
+        <v>43.5</v>
+      </c>
+      <c r="Q143" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="R143" s="88">
+        <f t="shared" ref="R143" si="63">AVERAGE(R136:R142)</f>
+        <v>92.285714285714292</v>
+      </c>
+      <c r="S143" s="88">
+        <v>3.9</v>
+      </c>
+      <c r="T143" s="88">
+        <v>0.4</v>
+      </c>
+      <c r="U143" s="88">
+        <v>3.5</v>
+      </c>
+      <c r="V143" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="W143" s="88">
+        <v>0</v>
+      </c>
+      <c r="X143" s="88">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y143" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:28">
       <c r="B144" s="7" t="s">
         <v>41</v>
       </c>
@@ -26908,7 +29310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:25">
       <c r="B145" s="7" t="s">
         <v>40</v>
       </c>
@@ -26943,8 +29345,11 @@
       <c r="L145" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:12">
+      <c r="N145" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25">
       <c r="B146" s="7" t="s">
         <v>39</v>
       </c>
@@ -26979,8 +29384,44 @@
       <c r="L146" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:12">
+      <c r="N146" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O146" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="P146" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q146" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="R146" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S146" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="T146" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U146" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="V146" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="W146" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="X146" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y146" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25">
       <c r="B147" s="7" t="s">
         <v>38</v>
       </c>
@@ -27015,53 +29456,244 @@
       <c r="L147" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:12">
+      <c r="N147" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O147" s="88">
+        <v>53.5</v>
+      </c>
+      <c r="P147" s="88">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="Q147" s="88">
+        <v>0</v>
+      </c>
+      <c r="R147" s="51">
+        <f>SUM(O147:Q147)</f>
+        <v>91.3</v>
+      </c>
+      <c r="S147" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="T147" s="88">
+        <v>0</v>
+      </c>
+      <c r="U147" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="V147" s="88">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="W147" s="88">
+        <v>0.4</v>
+      </c>
+      <c r="X147" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="Y147" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25">
       <c r="B148" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C148" s="7">
-        <f t="shared" ref="C148:L148" si="46">AVERAGE(C143:C147)</f>
+        <f t="shared" ref="C148:L148" si="64">AVERAGE(C143:C147)</f>
         <v>79.540000000000006</v>
       </c>
       <c r="D148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>8.58</v>
       </c>
       <c r="E148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>3.3200000000000003</v>
       </c>
       <c r="F148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>91.439999999999984</v>
       </c>
       <c r="G148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>3.88</v>
       </c>
       <c r="H148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>6.0000000000000012E-2</v>
       </c>
       <c r="J148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>3.3200000000000003</v>
       </c>
       <c r="K148" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="L148" s="7">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="N148" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O148" s="88">
+        <v>48.7</v>
+      </c>
+      <c r="P148" s="88">
+        <v>30.9</v>
+      </c>
+      <c r="Q148" s="88">
+        <v>0</v>
+      </c>
+      <c r="R148" s="51">
+        <f t="shared" ref="R148:R153" si="65">SUM(O148:Q148)</f>
+        <v>79.599999999999994</v>
+      </c>
+      <c r="S148" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="T148" s="88">
+        <v>0</v>
+      </c>
+      <c r="U148" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="V148" s="88">
+        <v>15.6</v>
+      </c>
+      <c r="W148" s="88">
+        <v>1.4</v>
+      </c>
+      <c r="X148" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="Y148" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25">
+      <c r="N149" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O149" s="88">
+        <v>72.8</v>
+      </c>
+      <c r="P149" s="88">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="Q149" s="88">
+        <v>0.9</v>
+      </c>
+      <c r="R149" s="51">
+        <f t="shared" si="65"/>
+        <v>90.1</v>
+      </c>
+      <c r="S149" s="88">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="T149" s="88">
+        <v>0</v>
+      </c>
+      <c r="U149" s="88">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V149" s="88">
+        <v>3.2</v>
+      </c>
+      <c r="W149" s="88">
+        <v>0.4</v>
+      </c>
+      <c r="X149" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="Y149" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25">
+      <c r="N150" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O150" s="88">
+        <v>66.8</v>
+      </c>
+      <c r="P150" s="88">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="Q150" s="88">
+        <v>0.7</v>
+      </c>
+      <c r="R150" s="51">
+        <f t="shared" si="65"/>
+        <v>87.399999999999991</v>
+      </c>
+      <c r="S150" s="88">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="T150" s="88">
+        <v>0</v>
+      </c>
+      <c r="U150" s="88">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V150" s="88">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="W150" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="X150" s="88">
+        <v>1.6</v>
+      </c>
+      <c r="Y150" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25">
+      <c r="N151" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O151" s="88">
+        <v>58.8</v>
+      </c>
+      <c r="P151" s="88">
+        <v>29.8</v>
+      </c>
+      <c r="Q151" s="88">
+        <v>0</v>
+      </c>
+      <c r="R151" s="51">
+        <f t="shared" si="65"/>
+        <v>88.6</v>
+      </c>
+      <c r="S151" s="88">
+        <v>4</v>
+      </c>
+      <c r="T151" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="U151" s="88">
+        <v>3.8</v>
+      </c>
+      <c r="V151" s="88">
+        <v>6.3</v>
+      </c>
+      <c r="W151" s="88">
+        <v>0.3</v>
+      </c>
+      <c r="X151" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="Y151" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25">
       <c r="A152" s="1" t="s">
         <v>2</v>
       </c>
@@ -27098,8 +29730,45 @@
       <c r="L152" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="153" spans="1:12">
+      <c r="N152" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O152" s="88">
+        <v>49.3</v>
+      </c>
+      <c r="P152" s="88">
+        <v>45.3</v>
+      </c>
+      <c r="Q152" s="88">
+        <v>0</v>
+      </c>
+      <c r="R152" s="51">
+        <f t="shared" si="65"/>
+        <v>94.6</v>
+      </c>
+      <c r="S152" s="88">
+        <v>0</v>
+      </c>
+      <c r="T152" s="88">
+        <v>0</v>
+      </c>
+      <c r="U152" s="88">
+        <v>0</v>
+      </c>
+      <c r="V152" s="88">
+        <v>3.3</v>
+      </c>
+      <c r="W152" s="88">
+        <v>0</v>
+      </c>
+      <c r="X152" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="Y152" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25">
       <c r="B153" s="7" t="s">
         <v>42</v>
       </c>
@@ -27134,8 +29803,45 @@
       <c r="L153" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:12">
+      <c r="N153" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O153" s="88">
+        <v>0</v>
+      </c>
+      <c r="P153" s="88">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="88">
+        <v>0</v>
+      </c>
+      <c r="R153" s="51">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="S153" s="88">
+        <v>0</v>
+      </c>
+      <c r="T153" s="88">
+        <v>0</v>
+      </c>
+      <c r="U153" s="88">
+        <v>0</v>
+      </c>
+      <c r="V153" s="88">
+        <v>0</v>
+      </c>
+      <c r="W153" s="88">
+        <v>0</v>
+      </c>
+      <c r="X153" s="88">
+        <v>100</v>
+      </c>
+      <c r="Y153" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25">
       <c r="B154" s="7" t="s">
         <v>41</v>
       </c>
@@ -27170,8 +29876,45 @@
       <c r="L154" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:12">
+      <c r="N154" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O154" s="88">
+        <v>50</v>
+      </c>
+      <c r="P154" s="88">
+        <v>25.7</v>
+      </c>
+      <c r="Q154" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="R154" s="88">
+        <f t="shared" ref="R154" si="66">AVERAGE(R147:R153)</f>
+        <v>75.94285714285715</v>
+      </c>
+      <c r="S154" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T154" s="88">
+        <v>0</v>
+      </c>
+      <c r="U154" s="88">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="V154" s="88">
+        <v>5.4</v>
+      </c>
+      <c r="W154" s="88">
+        <v>0.4</v>
+      </c>
+      <c r="X154" s="88">
+        <v>15.5</v>
+      </c>
+      <c r="Y154" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25">
       <c r="B155" s="7" t="s">
         <v>40</v>
       </c>
@@ -27207,7 +29950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:25">
       <c r="B156" s="7" t="s">
         <v>39</v>
       </c>
@@ -27242,8 +29985,11 @@
       <c r="L156" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:12">
+      <c r="N156" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25">
       <c r="B157" s="7" t="s">
         <v>38</v>
       </c>
@@ -27278,55 +30024,484 @@
       <c r="L157" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:12">
+      <c r="N157" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O157" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="P157" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q157" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="R157" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S157" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="T157" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="U157" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V157" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="W157" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X157" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y157" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25">
       <c r="B158" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C158" s="7">
-        <f t="shared" ref="C158:L158" si="47">AVERAGE(C153:C157)</f>
+        <f t="shared" ref="C158:L158" si="67">AVERAGE(C153:C157)</f>
         <v>79.459999999999994</v>
       </c>
       <c r="D158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>6.8400000000000007</v>
       </c>
       <c r="E158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>2.8</v>
       </c>
       <c r="F158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>89.1</v>
       </c>
       <c r="G158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>5.78</v>
       </c>
       <c r="H158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="I158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>0.74</v>
       </c>
       <c r="J158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>3.7399999999999998</v>
       </c>
       <c r="K158" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="L158" s="7">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="N158" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O158" s="88">
+        <f>AVERAGE(O147,O136,O125)</f>
+        <v>44.666666666666664</v>
+      </c>
+      <c r="P158" s="88">
+        <f t="shared" ref="P158:S158" si="68">AVERAGE(P147,P136,P125)</f>
+        <v>49.566666666666663</v>
+      </c>
+      <c r="Q158" s="88">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="R158" s="51">
+        <f>SUM(O158:Q158)</f>
+        <v>94.23333333333332</v>
+      </c>
+      <c r="S158" s="88">
+        <f t="shared" ref="S158:Y158" si="69">AVERAGE(S147,S136,S125)</f>
+        <v>1.1333333333333335</v>
+      </c>
+      <c r="T158" s="88">
+        <f t="shared" si="69"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="U158" s="88">
+        <f t="shared" si="69"/>
+        <v>0.6</v>
+      </c>
+      <c r="V158" s="88">
+        <f t="shared" si="69"/>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="W158" s="88">
+        <f t="shared" si="69"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="X158" s="88">
+        <f t="shared" si="69"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="Y158" s="88">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25">
+      <c r="N159" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O159" s="88">
+        <f t="shared" ref="O159:Q159" si="70">AVERAGE(O148,O137,O126)</f>
+        <v>49.266666666666673</v>
+      </c>
+      <c r="P159" s="88">
+        <f t="shared" si="70"/>
+        <v>38.366666666666667</v>
+      </c>
+      <c r="Q159" s="88">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="R159" s="51">
+        <f t="shared" ref="R159:R164" si="71">SUM(O159:Q159)</f>
+        <v>87.63333333333334</v>
+      </c>
+      <c r="S159" s="88">
+        <f t="shared" ref="S159:Y159" si="72">AVERAGE(S148,S137,S126)</f>
+        <v>2</v>
+      </c>
+      <c r="T159" s="88">
+        <f t="shared" si="72"/>
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="U159" s="88">
+        <f t="shared" si="72"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="V159" s="88">
+        <f t="shared" si="72"/>
+        <v>5.9666666666666659</v>
+      </c>
+      <c r="W159" s="88">
+        <f t="shared" si="72"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="X159" s="88">
+        <f t="shared" si="72"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="Y159" s="88">
+        <f t="shared" si="72"/>
+        <v>3.0666666666666664</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25">
+      <c r="N160" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O160" s="88">
+        <f t="shared" ref="O160:Q160" si="73">AVERAGE(O149,O138,O127)</f>
+        <v>68.066666666666663</v>
+      </c>
+      <c r="P160" s="88">
+        <f t="shared" si="73"/>
+        <v>23.7</v>
+      </c>
+      <c r="Q160" s="88">
+        <f t="shared" si="73"/>
+        <v>0.6</v>
+      </c>
+      <c r="R160" s="51">
+        <f t="shared" si="71"/>
+        <v>92.36666666666666</v>
+      </c>
+      <c r="S160" s="88">
+        <f t="shared" ref="S160:Y160" si="74">AVERAGE(S149,S138,S127)</f>
+        <v>4</v>
+      </c>
+      <c r="T160" s="88">
+        <f t="shared" si="74"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U160" s="88">
+        <f t="shared" si="74"/>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="V160" s="88">
+        <f t="shared" si="74"/>
+        <v>2.7000000000000006</v>
+      </c>
+      <c r="W160" s="88">
+        <f t="shared" si="74"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="X160" s="88">
+        <f t="shared" si="74"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="Y160" s="88">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="14:25">
+      <c r="N161" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O161" s="88">
+        <f t="shared" ref="O161:Q161" si="75">AVERAGE(O150,O139,O128)</f>
+        <v>63.766666666666673</v>
+      </c>
+      <c r="P161" s="88">
+        <f t="shared" si="75"/>
+        <v>24.966666666666669</v>
+      </c>
+      <c r="Q161" s="88">
+        <f t="shared" si="75"/>
+        <v>0.93333333333333324</v>
+      </c>
+      <c r="R161" s="51">
+        <f t="shared" si="71"/>
+        <v>89.666666666666686</v>
+      </c>
+      <c r="S161" s="88">
+        <f t="shared" ref="S161:Y161" si="76">AVERAGE(S150,S139,S128)</f>
+        <v>5.8666666666666671</v>
+      </c>
+      <c r="T161" s="88">
+        <f t="shared" si="76"/>
+        <v>0.23333333333333331</v>
+      </c>
+      <c r="U161" s="88">
+        <f t="shared" si="76"/>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="V161" s="88">
+        <f t="shared" si="76"/>
+        <v>3.4666666666666668</v>
+      </c>
+      <c r="W161" s="88">
+        <f t="shared" si="76"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="X161" s="88">
+        <f t="shared" si="76"/>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="Y161" s="88">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="14:25">
+      <c r="N162" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O162" s="88">
+        <f t="shared" ref="O162:Q162" si="77">AVERAGE(O151,O140,O129)</f>
+        <v>53</v>
+      </c>
+      <c r="P162" s="88">
+        <f t="shared" si="77"/>
+        <v>37.866666666666667</v>
+      </c>
+      <c r="Q162" s="88">
+        <f>AVERAGE(Q151,Q140,Q129)</f>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="R162" s="51">
+        <f t="shared" si="71"/>
+        <v>91.4</v>
+      </c>
+      <c r="S162" s="88">
+        <f t="shared" ref="S162:Y162" si="78">AVERAGE(S151,S140,S129)</f>
+        <v>4.2333333333333334</v>
+      </c>
+      <c r="T162" s="88">
+        <f t="shared" si="78"/>
+        <v>1.4333333333333333</v>
+      </c>
+      <c r="U162" s="88">
+        <f t="shared" si="78"/>
+        <v>2.7666666666666671</v>
+      </c>
+      <c r="V162" s="88">
+        <f t="shared" si="78"/>
+        <v>3.7333333333333338</v>
+      </c>
+      <c r="W162" s="88">
+        <f t="shared" si="78"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="X162" s="88">
+        <f t="shared" si="78"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="Y162" s="88">
+        <f t="shared" si="78"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="14:25">
+      <c r="N163" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O163" s="88">
+        <f t="shared" ref="O163:Q163" si="79">AVERAGE(O152,O141,O130)</f>
+        <v>31.066666666666663</v>
+      </c>
+      <c r="P163" s="88">
+        <f t="shared" si="79"/>
+        <v>66.833333333333329</v>
+      </c>
+      <c r="Q163" s="88">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="R163" s="51">
+        <f t="shared" si="71"/>
+        <v>97.899999999999991</v>
+      </c>
+      <c r="S163" s="88">
+        <f t="shared" ref="S163:Y163" si="80">AVERAGE(S152,S141,S130)</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="T163" s="88">
+        <f t="shared" si="80"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="U163" s="88">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="V163" s="88">
+        <f t="shared" si="80"/>
+        <v>1.0999999999999999</v>
+      </c>
+      <c r="W163" s="88">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="X163" s="88">
+        <f t="shared" si="80"/>
+        <v>0.6</v>
+      </c>
+      <c r="Y163" s="88">
+        <f t="shared" si="80"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="14:25">
+      <c r="N164" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="O164" s="88">
+        <f t="shared" ref="O164:Q164" si="81">AVERAGE(O153,O142,O131)</f>
+        <v>20.133333333333333</v>
+      </c>
+      <c r="P164" s="88">
+        <f t="shared" si="81"/>
+        <v>33.733333333333334</v>
+      </c>
+      <c r="Q164" s="88">
+        <f t="shared" si="81"/>
+        <v>0.39999999999999997</v>
+      </c>
+      <c r="R164" s="51">
+        <f t="shared" si="71"/>
+        <v>54.266666666666666</v>
+      </c>
+      <c r="S164" s="88">
+        <f t="shared" ref="S164:Y164" si="82">AVERAGE(S153,S142,S131)</f>
+        <v>6.3666666666666671</v>
+      </c>
+      <c r="T164" s="88">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="U164" s="88">
+        <f t="shared" si="82"/>
+        <v>6.3666666666666671</v>
+      </c>
+      <c r="V164" s="88">
+        <f t="shared" si="82"/>
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="W164" s="88">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="X164" s="88">
+        <f t="shared" si="82"/>
+        <v>38.5</v>
+      </c>
+      <c r="Y164" s="88">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="14:25">
+      <c r="N165" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O165" s="88">
+        <f>AVERAGE(O158:O164)</f>
+        <v>47.138095238095232</v>
+      </c>
+      <c r="P165" s="88">
+        <f t="shared" ref="P165:Y165" si="83">AVERAGE(P158:P164)</f>
+        <v>39.290476190476191</v>
+      </c>
+      <c r="Q165" s="88">
+        <f t="shared" si="83"/>
+        <v>0.35238095238095235</v>
+      </c>
+      <c r="R165" s="88">
+        <f t="shared" si="83"/>
+        <v>86.780952380952385</v>
+      </c>
+      <c r="S165" s="88">
+        <f t="shared" si="83"/>
+        <v>3.3904761904761904</v>
+      </c>
+      <c r="T165" s="88">
+        <f t="shared" si="83"/>
+        <v>0.44761904761904764</v>
+      </c>
+      <c r="U165" s="88">
+        <f t="shared" si="83"/>
+        <v>2.9238095238095241</v>
+      </c>
+      <c r="V165" s="88">
+        <f t="shared" si="83"/>
+        <v>3.0523809523809531</v>
+      </c>
+      <c r="W165" s="88">
+        <f t="shared" si="83"/>
+        <v>0.16190476190476194</v>
+      </c>
+      <c r="X165" s="88">
+        <f t="shared" si="83"/>
+        <v>5.9190476190476193</v>
+      </c>
+      <c r="Y165" s="88">
+        <f t="shared" si="83"/>
+        <v>0.46190476190476193</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="R114 R115:R120 R158:R159 R160:R164" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
